--- a/numbers.xlsx
+++ b/numbers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nurmu\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nodir\Projects\open-budget-search\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0957085C-C532-45E9-9178-12F52DBC8351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CAC716-B4CB-4779-9F69-75DB3CA82D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0AABE945-EFF0-4E0B-A9BD-4BB876D9C82D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="951">
   <si>
     <t>**-*14-63-61</t>
   </si>
@@ -2332,6 +2332,561 @@
   </si>
   <si>
     <t>**-*64-34-39</t>
+  </si>
+  <si>
+    <t>**-*85-39-69</t>
+  </si>
+  <si>
+    <t>**-*61-00-74</t>
+  </si>
+  <si>
+    <t>**-*20-06-91</t>
+  </si>
+  <si>
+    <t>**-*24-08-11</t>
+  </si>
+  <si>
+    <t>**-*31-89-91</t>
+  </si>
+  <si>
+    <t>**-*36-01-95</t>
+  </si>
+  <si>
+    <t>**-*09-11-23</t>
+  </si>
+  <si>
+    <t>**-*11-98-96</t>
+  </si>
+  <si>
+    <t>**-*78-11-99</t>
+  </si>
+  <si>
+    <t>**-*93-66-69</t>
+  </si>
+  <si>
+    <t>**-*15-01-37</t>
+  </si>
+  <si>
+    <t>**-*47-77-96</t>
+  </si>
+  <si>
+    <t>**-*74-14-99</t>
+  </si>
+  <si>
+    <t>**-*90-45-48</t>
+  </si>
+  <si>
+    <t>**-*86-59-19</t>
+  </si>
+  <si>
+    <t>**-*56-77-97</t>
+  </si>
+  <si>
+    <t>**-*50-03-18</t>
+  </si>
+  <si>
+    <t>**-*95-66-69</t>
+  </si>
+  <si>
+    <t>**-*40-45-92</t>
+  </si>
+  <si>
+    <t>**-*69-29-95</t>
+  </si>
+  <si>
+    <t>**-*50-94-89</t>
+  </si>
+  <si>
+    <t>**-*02-83-00</t>
+  </si>
+  <si>
+    <t>**-*83-86-24</t>
+  </si>
+  <si>
+    <t>**-*00-42-47</t>
+  </si>
+  <si>
+    <t>**-*60-36-43</t>
+  </si>
+  <si>
+    <t>**-*73-89-93</t>
+  </si>
+  <si>
+    <t>**-*61-10-53</t>
+  </si>
+  <si>
+    <t>**-*37-11-96</t>
+  </si>
+  <si>
+    <t>**-*47-83-23</t>
+  </si>
+  <si>
+    <t>**-*86-79-65</t>
+  </si>
+  <si>
+    <t>**-*63-05-85</t>
+  </si>
+  <si>
+    <t>**-*21-90-84</t>
+  </si>
+  <si>
+    <t>**-*25-25-38</t>
+  </si>
+  <si>
+    <t>**-*98-89-85</t>
+  </si>
+  <si>
+    <t>**-*97-93-24</t>
+  </si>
+  <si>
+    <t>**-*54-03-04</t>
+  </si>
+  <si>
+    <t>**-*86-02-17</t>
+  </si>
+  <si>
+    <t>**-*01-10-74</t>
+  </si>
+  <si>
+    <t>**-*81-69-71</t>
+  </si>
+  <si>
+    <t>**-*23-18-15</t>
+  </si>
+  <si>
+    <t>**-*28-96-01</t>
+  </si>
+  <si>
+    <t>**-*34-46-36</t>
+  </si>
+  <si>
+    <t>**-*89-10-49</t>
+  </si>
+  <si>
+    <t>**-*91-93-85</t>
+  </si>
+  <si>
+    <t>**-*19-98-95</t>
+  </si>
+  <si>
+    <t>**-*96-11-09</t>
+  </si>
+  <si>
+    <t>**-*56-98-04</t>
+  </si>
+  <si>
+    <t>**-*21-19-21</t>
+  </si>
+  <si>
+    <t>**-*69-42-88</t>
+  </si>
+  <si>
+    <t>**-*08-01-33</t>
+  </si>
+  <si>
+    <t>**-*16-27-80</t>
+  </si>
+  <si>
+    <t>**-*73-10-61</t>
+  </si>
+  <si>
+    <t>**-*19-79-99</t>
+  </si>
+  <si>
+    <t>**-*57-67-07</t>
+  </si>
+  <si>
+    <t>**-*00-27-80</t>
+  </si>
+  <si>
+    <t>**-*05-08-86</t>
+  </si>
+  <si>
+    <t>**-*55-21-56</t>
+  </si>
+  <si>
+    <t>**-*21-74-12</t>
+  </si>
+  <si>
+    <t>**-*46-88-07</t>
+  </si>
+  <si>
+    <t>**-*36-26-20</t>
+  </si>
+  <si>
+    <t>**-*01-20-68</t>
+  </si>
+  <si>
+    <t>**-*95-99-98</t>
+  </si>
+  <si>
+    <t>**-*21-26-45</t>
+  </si>
+  <si>
+    <t>**-*19-83-86</t>
+  </si>
+  <si>
+    <t>**-*51-42-29</t>
+  </si>
+  <si>
+    <t>**-*11-29-09</t>
+  </si>
+  <si>
+    <t>**-*05-51-91</t>
+  </si>
+  <si>
+    <t>**-*36-19-29</t>
+  </si>
+  <si>
+    <t>**-*14-06-86</t>
+  </si>
+  <si>
+    <t>**-*15-20-88</t>
+  </si>
+  <si>
+    <t>**-*76-18-02</t>
+  </si>
+  <si>
+    <t>**-*59-58-56</t>
+  </si>
+  <si>
+    <t>**-*27-06-96</t>
+  </si>
+  <si>
+    <t>**-*22-12-83</t>
+  </si>
+  <si>
+    <t>**-*71-79-96</t>
+  </si>
+  <si>
+    <t>**-*15-90-30</t>
+  </si>
+  <si>
+    <t>**-*00-78-96</t>
+  </si>
+  <si>
+    <t>**-*53-97-37</t>
+  </si>
+  <si>
+    <t>**-*07-04-26</t>
+  </si>
+  <si>
+    <t>**-*08-80-67</t>
+  </si>
+  <si>
+    <t>**-*35-22-54</t>
+  </si>
+  <si>
+    <t>**-*38-07-23</t>
+  </si>
+  <si>
+    <t>**-*35-79-92</t>
+  </si>
+  <si>
+    <t>**-*00-25-10</t>
+  </si>
+  <si>
+    <t>**-*49-07-34</t>
+  </si>
+  <si>
+    <t>**-*99-44-00</t>
+  </si>
+  <si>
+    <t>**-*10-87-00</t>
+  </si>
+  <si>
+    <t>**-*72-21-24</t>
+  </si>
+  <si>
+    <t>**-*18-10-82</t>
+  </si>
+  <si>
+    <t>**-*50-87-85</t>
+  </si>
+  <si>
+    <t>**-*70-28-86</t>
+  </si>
+  <si>
+    <t>**-*93-89-04</t>
+  </si>
+  <si>
+    <t>**-*16-70-17</t>
+  </si>
+  <si>
+    <t>**-*17-95-99</t>
+  </si>
+  <si>
+    <t>**-*96-10-94</t>
+  </si>
+  <si>
+    <t>**-*60-95-99</t>
+  </si>
+  <si>
+    <t>**-*37-87-71</t>
+  </si>
+  <si>
+    <t>**-*59-94-74</t>
+  </si>
+  <si>
+    <t>**-*55-26-87</t>
+  </si>
+  <si>
+    <t>**-*48-61-26</t>
+  </si>
+  <si>
+    <t>**-*28-10-26</t>
+  </si>
+  <si>
+    <t>**-*91-70-06</t>
+  </si>
+  <si>
+    <t>**-*72-33-99</t>
+  </si>
+  <si>
+    <t>**-*79-43-83</t>
+  </si>
+  <si>
+    <t>**-*16-10-25</t>
+  </si>
+  <si>
+    <t>**-*72-60-45</t>
+  </si>
+  <si>
+    <t>**-*50-15-14</t>
+  </si>
+  <si>
+    <t>**-*14-51-00</t>
+  </si>
+  <si>
+    <t>**-*36-05-67</t>
+  </si>
+  <si>
+    <t>**-*98-08-24</t>
+  </si>
+  <si>
+    <t>**-*09-39-31</t>
+  </si>
+  <si>
+    <t>**-*71-26-07</t>
+  </si>
+  <si>
+    <t>**-*79-17-18</t>
+  </si>
+  <si>
+    <t>**-*30-34-88</t>
+  </si>
+  <si>
+    <t>**-*21-81-72</t>
+  </si>
+  <si>
+    <t>**-*73-98-99</t>
+  </si>
+  <si>
+    <t>**-*53-22-44</t>
+  </si>
+  <si>
+    <t>**-*56-04-77</t>
+  </si>
+  <si>
+    <t>**-*00-01-72</t>
+  </si>
+  <si>
+    <t>**-*37-54-08</t>
+  </si>
+  <si>
+    <t>**-*70-74-55</t>
+  </si>
+  <si>
+    <t>**-*38-27-47</t>
+  </si>
+  <si>
+    <t>**-*22-13-06</t>
+  </si>
+  <si>
+    <t>**-*95-11-73</t>
+  </si>
+  <si>
+    <t>**-*53-60-50</t>
+  </si>
+  <si>
+    <t>**-*72-98-94</t>
+  </si>
+  <si>
+    <t>**-*43-03-07</t>
+  </si>
+  <si>
+    <t>**-*18-80-76</t>
+  </si>
+  <si>
+    <t>**-*77-60-38</t>
+  </si>
+  <si>
+    <t>**-*16-70-76</t>
+  </si>
+  <si>
+    <t>**-*12-49-97</t>
+  </si>
+  <si>
+    <t>**-*93-26-09</t>
+  </si>
+  <si>
+    <t>**-*05-70-35</t>
+  </si>
+  <si>
+    <t>**-*71-07-87</t>
+  </si>
+  <si>
+    <t>**-*10-70-58</t>
+  </si>
+  <si>
+    <t>**-*58-57-69</t>
+  </si>
+  <si>
+    <t>**-*43-33-91</t>
+  </si>
+  <si>
+    <t>**-*94-22-33</t>
+  </si>
+  <si>
+    <t>**-*50-50-07</t>
+  </si>
+  <si>
+    <t>**-*80-00-79</t>
+  </si>
+  <si>
+    <t>**-*44-19-33</t>
+  </si>
+  <si>
+    <t>**-*24-85-04</t>
+  </si>
+  <si>
+    <t>**-*08-97-15</t>
+  </si>
+  <si>
+    <t>**-*29-01-57</t>
+  </si>
+  <si>
+    <t>**-*79-22-32</t>
+  </si>
+  <si>
+    <t>**-*22-68-81</t>
+  </si>
+  <si>
+    <t>**-*13-41-61</t>
+  </si>
+  <si>
+    <t>**-*78-12-16</t>
+  </si>
+  <si>
+    <t>**-*73-80-24</t>
+  </si>
+  <si>
+    <t>**-*65-91-99</t>
+  </si>
+  <si>
+    <t>**-*03-89-99</t>
+  </si>
+  <si>
+    <t>**-*20-02-09</t>
+  </si>
+  <si>
+    <t>**-*48-90-02</t>
+  </si>
+  <si>
+    <t>**-*50-97-08</t>
+  </si>
+  <si>
+    <t>**-*86-86-01</t>
+  </si>
+  <si>
+    <t>**-*09-29-89</t>
+  </si>
+  <si>
+    <t>**-*06-45-67</t>
+  </si>
+  <si>
+    <t>**-*48-87-84</t>
+  </si>
+  <si>
+    <t>**-*86-00-71</t>
+  </si>
+  <si>
+    <t>**-*45-74-28</t>
+  </si>
+  <si>
+    <t>**-*61-09-04</t>
+  </si>
+  <si>
+    <t>**-*38-70-38</t>
+  </si>
+  <si>
+    <t>**-*74-54-81</t>
+  </si>
+  <si>
+    <t>**-*11-83-87</t>
+  </si>
+  <si>
+    <t>**-*08-29-97</t>
+  </si>
+  <si>
+    <t>**-*77-30-77</t>
+  </si>
+  <si>
+    <t>**-*82-86-18</t>
+  </si>
+  <si>
+    <t>**-*56-63-30</t>
+  </si>
+  <si>
+    <t>**-*95-95-08</t>
+  </si>
+  <si>
+    <t>**-*00-61-59</t>
+  </si>
+  <si>
+    <t>**-*19-11-81</t>
+  </si>
+  <si>
+    <t>**-*99-89-56</t>
+  </si>
+  <si>
+    <t>**-*33-70-69</t>
+  </si>
+  <si>
+    <t>**-*14-47-27</t>
+  </si>
+  <si>
+    <t>**-*71-09-21</t>
+  </si>
+  <si>
+    <t>**-*48-18-89</t>
+  </si>
+  <si>
+    <t>**-*29-13-94</t>
+  </si>
+  <si>
+    <t>**-*93-01-88</t>
+  </si>
+  <si>
+    <t>**-*50-35-70</t>
+  </si>
+  <si>
+    <t>**-*19-28-29</t>
+  </si>
+  <si>
+    <t>**-*19-00-74</t>
+  </si>
+  <si>
+    <t>**-*11-80-18</t>
+  </si>
+  <si>
+    <t>**-*02-82-85</t>
+  </si>
+  <si>
+    <t>**-*17-33-74</t>
+  </si>
+  <si>
+    <t>**-*56-66-20</t>
   </si>
 </sst>
 </file>
@@ -2773,7 +3328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA66EC08-8D26-46AA-A6AA-1D6A0B4C73D5}">
-  <dimension ref="A7:C787"/>
+  <dimension ref="A7:C973"/>
   <sheetFormatPr defaultRowHeight="21" thickBottom="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25.28515625" customWidth="1"/>
@@ -11371,6 +11926,2041 @@
         <v>46092.009027777778</v>
       </c>
     </row>
+    <row r="789" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A789" s="3">
+        <v>1</v>
+      </c>
+      <c r="B789" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="C789" s="5">
+        <v>46093.642361111109</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A790" s="4">
+        <v>2</v>
+      </c>
+      <c r="B790" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C790" s="5">
+        <v>46093.640972222223</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A791" s="4">
+        <v>3</v>
+      </c>
+      <c r="B791" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="C791" s="5">
+        <v>46093.640972222223</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A792" s="4">
+        <v>4</v>
+      </c>
+      <c r="B792" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C792" s="5">
+        <v>46093.640277777777</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A793" s="4">
+        <v>5</v>
+      </c>
+      <c r="B793" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C793" s="5">
+        <v>46093.640277777777</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A794" s="4">
+        <v>6</v>
+      </c>
+      <c r="B794" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C794" s="5">
+        <v>46093.638194444444</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A795" s="4">
+        <v>7</v>
+      </c>
+      <c r="B795" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C795" s="5">
+        <v>46093.637499999997</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A796" s="4">
+        <v>8</v>
+      </c>
+      <c r="B796" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C796" s="5">
+        <v>46093.637499999997</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A797" s="4">
+        <v>9</v>
+      </c>
+      <c r="B797" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="C797" s="5">
+        <v>46093.631944444445</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A798" s="4">
+        <v>10</v>
+      </c>
+      <c r="B798" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="C798" s="5">
+        <v>46093.629166666666</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A799" s="4">
+        <v>11</v>
+      </c>
+      <c r="B799" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="C799" s="5">
+        <v>46093.628472222219</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A800" s="4">
+        <v>12</v>
+      </c>
+      <c r="B800" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C800" s="5">
+        <v>46093.625694444447</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A801" s="3">
+        <v>13</v>
+      </c>
+      <c r="B801" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="C801" s="5">
+        <v>46093.623611111114</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A802" s="4">
+        <v>14</v>
+      </c>
+      <c r="B802" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C802" s="5">
+        <v>46093.621527777781</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A803" s="4">
+        <v>15</v>
+      </c>
+      <c r="B803" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="C803" s="5">
+        <v>46093.621527777781</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A804" s="4">
+        <v>16</v>
+      </c>
+      <c r="B804" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C804" s="5">
+        <v>46093.621527777781</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A805" s="4">
+        <v>17</v>
+      </c>
+      <c r="B805" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="C805" s="5">
+        <v>46093.620138888888</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A806" s="4">
+        <v>18</v>
+      </c>
+      <c r="B806" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C806" s="5">
+        <v>46093.618055555555</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A807" s="4">
+        <v>19</v>
+      </c>
+      <c r="B807" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C807" s="5">
+        <v>46093.617361111108</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A808" s="4">
+        <v>20</v>
+      </c>
+      <c r="B808" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C808" s="5">
+        <v>46093.615972222222</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A809" s="4">
+        <v>21</v>
+      </c>
+      <c r="B809" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="C809" s="5">
+        <v>46093.613194444442</v>
+      </c>
+    </row>
+    <row r="810" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A810" s="4">
+        <v>22</v>
+      </c>
+      <c r="B810" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C810" s="5">
+        <v>46093.612500000003</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A811" s="4">
+        <v>23</v>
+      </c>
+      <c r="B811" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C811" s="5">
+        <v>46093.611805555556</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A812" s="4">
+        <v>24</v>
+      </c>
+      <c r="B812" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C812" s="5">
+        <v>46093.611111111109</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A813" s="3">
+        <v>25</v>
+      </c>
+      <c r="B813" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="C813" s="5">
+        <v>46093.61041666667</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A814" s="4">
+        <v>26</v>
+      </c>
+      <c r="B814" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C814" s="5">
+        <v>46093.609027777777</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A815" s="4">
+        <v>27</v>
+      </c>
+      <c r="B815" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C815" s="5">
+        <v>46093.609027777777</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A816" s="4">
+        <v>28</v>
+      </c>
+      <c r="B816" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C816" s="5">
+        <v>46093.60833333333</v>
+      </c>
+    </row>
+    <row r="817" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A817" s="4">
+        <v>29</v>
+      </c>
+      <c r="B817" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C817" s="5">
+        <v>46093.60833333333</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A818" s="4">
+        <v>30</v>
+      </c>
+      <c r="B818" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C818" s="5">
+        <v>46093.607638888891</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A819" s="4">
+        <v>31</v>
+      </c>
+      <c r="B819" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C819" s="5">
+        <v>46093.606249999997</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A820" s="4">
+        <v>32</v>
+      </c>
+      <c r="B820" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C820" s="5">
+        <v>46093.606249999997</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A821" s="4">
+        <v>33</v>
+      </c>
+      <c r="B821" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="C821" s="5">
+        <v>46093.605555555558</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A822" s="4">
+        <v>34</v>
+      </c>
+      <c r="B822" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C822" s="5">
+        <v>46093.605555555558</v>
+      </c>
+    </row>
+    <row r="823" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A823" s="4">
+        <v>35</v>
+      </c>
+      <c r="B823" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="C823" s="5">
+        <v>46093.605555555558</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A824" s="4">
+        <v>36</v>
+      </c>
+      <c r="B824" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C824" s="5">
+        <v>46093.604166666664</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A825" s="3">
+        <v>37</v>
+      </c>
+      <c r="B825" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="C825" s="5">
+        <v>46093.603472222225</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A826" s="4">
+        <v>38</v>
+      </c>
+      <c r="B826" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C826" s="5">
+        <v>46093.602083333331</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A827" s="4">
+        <v>39</v>
+      </c>
+      <c r="B827" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C827" s="5">
+        <v>46093.600694444445</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A828" s="4">
+        <v>40</v>
+      </c>
+      <c r="B828" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C828" s="5">
+        <v>46093.599999999999</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A829" s="4">
+        <v>41</v>
+      </c>
+      <c r="B829" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C829" s="5">
+        <v>46093.599305555559</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A830" s="4">
+        <v>42</v>
+      </c>
+      <c r="B830" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C830" s="5">
+        <v>46093.599305555559</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A831" s="4">
+        <v>43</v>
+      </c>
+      <c r="B831" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C831" s="5">
+        <v>46093.597916666666</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A832" s="4">
+        <v>44</v>
+      </c>
+      <c r="B832" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="C832" s="5">
+        <v>46093.59652777778</v>
+      </c>
+    </row>
+    <row r="833" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A833" s="4">
+        <v>45</v>
+      </c>
+      <c r="B833" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C833" s="5">
+        <v>46093.595138888886</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A834" s="4">
+        <v>46</v>
+      </c>
+      <c r="B834" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C834" s="5">
+        <v>46093.588888888888</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A835" s="4">
+        <v>47</v>
+      </c>
+      <c r="B835" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C835" s="5">
+        <v>46093.588888888888</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A836" s="4">
+        <v>48</v>
+      </c>
+      <c r="B836" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C836" s="5">
+        <v>46093.588888888888</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A837" s="3">
+        <v>49</v>
+      </c>
+      <c r="B837" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="C837" s="5">
+        <v>46093.586805555555</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A838" s="4">
+        <v>50</v>
+      </c>
+      <c r="B838" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C838" s="5">
+        <v>46093.584722222222</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A839" s="4">
+        <v>51</v>
+      </c>
+      <c r="B839" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C839" s="5">
+        <v>46093.584027777775</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A840" s="4">
+        <v>52</v>
+      </c>
+      <c r="B840" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C840" s="5">
+        <v>46093.583333333336</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A841" s="4">
+        <v>53</v>
+      </c>
+      <c r="B841" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C841" s="5">
+        <v>46093.581250000003</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A842" s="4">
+        <v>54</v>
+      </c>
+      <c r="B842" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C842" s="5">
+        <v>46093.57916666667</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A843" s="4">
+        <v>55</v>
+      </c>
+      <c r="B843" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C843" s="5">
+        <v>46093.577777777777</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A844" s="4">
+        <v>56</v>
+      </c>
+      <c r="B844" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C844" s="5">
+        <v>46093.573611111111</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A845" s="4">
+        <v>57</v>
+      </c>
+      <c r="B845" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C845" s="5">
+        <v>46093.570833333331</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A846" s="4">
+        <v>58</v>
+      </c>
+      <c r="B846" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C846" s="5">
+        <v>46093.570138888892</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A847" s="4">
+        <v>59</v>
+      </c>
+      <c r="B847" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C847" s="5">
+        <v>46093.569444444445</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A848" s="4">
+        <v>60</v>
+      </c>
+      <c r="B848" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C848" s="5">
+        <v>46093.565972222219</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A849" s="3">
+        <v>61</v>
+      </c>
+      <c r="B849" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="C849" s="5">
+        <v>46093.56527777778</v>
+      </c>
+    </row>
+    <row r="850" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A850" s="4">
+        <v>62</v>
+      </c>
+      <c r="B850" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C850" s="5">
+        <v>46093.564583333333</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A851" s="4">
+        <v>63</v>
+      </c>
+      <c r="B851" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C851" s="5">
+        <v>46093.563888888886</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A852" s="4">
+        <v>64</v>
+      </c>
+      <c r="B852" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C852" s="5">
+        <v>46093.558333333334</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A853" s="4">
+        <v>65</v>
+      </c>
+      <c r="B853" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C853" s="5">
+        <v>46093.556944444441</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A854" s="4">
+        <v>66</v>
+      </c>
+      <c r="B854" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C854" s="5">
+        <v>46093.555555555555</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A855" s="4">
+        <v>67</v>
+      </c>
+      <c r="B855" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C855" s="5">
+        <v>46093.552777777775</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A856" s="4">
+        <v>68</v>
+      </c>
+      <c r="B856" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C856" s="5">
+        <v>46093.551388888889</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A857" s="4">
+        <v>69</v>
+      </c>
+      <c r="B857" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="C857" s="5">
+        <v>46093.549305555556</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A858" s="4">
+        <v>70</v>
+      </c>
+      <c r="B858" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C858" s="5">
+        <v>46093.548611111109</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A859" s="4">
+        <v>71</v>
+      </c>
+      <c r="B859" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C859" s="5">
+        <v>46093.548611111109</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A860" s="4">
+        <v>72</v>
+      </c>
+      <c r="B860" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="C860" s="5">
+        <v>46093.548611111109</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A861" s="3">
+        <v>73</v>
+      </c>
+      <c r="B861" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="C861" s="5">
+        <v>46093.54791666667</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A862" s="4">
+        <v>74</v>
+      </c>
+      <c r="B862" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="C862" s="5">
+        <v>46093.547222222223</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A863" s="4">
+        <v>75</v>
+      </c>
+      <c r="B863" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="C863" s="5">
+        <v>46093.547222222223</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A864" s="4">
+        <v>76</v>
+      </c>
+      <c r="B864" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="C864" s="5">
+        <v>46093.54583333333</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A865" s="4">
+        <v>77</v>
+      </c>
+      <c r="B865" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="C865" s="5">
+        <v>46093.542361111111</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A866" s="4">
+        <v>78</v>
+      </c>
+      <c r="B866" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="C866" s="5">
+        <v>46093.541666666664</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A867" s="4">
+        <v>79</v>
+      </c>
+      <c r="B867" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="C867" s="5">
+        <v>46093.541666666664</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A868" s="4">
+        <v>80</v>
+      </c>
+      <c r="B868" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="C868" s="5">
+        <v>46093.539583333331</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A869" s="4">
+        <v>81</v>
+      </c>
+      <c r="B869" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="C869" s="5">
+        <v>46093.536111111112</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A870" s="4">
+        <v>82</v>
+      </c>
+      <c r="B870" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="C870" s="5">
+        <v>46093.526388888888</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A871" s="4">
+        <v>83</v>
+      </c>
+      <c r="B871" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C871" s="5">
+        <v>46093.523611111108</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A872" s="4">
+        <v>84</v>
+      </c>
+      <c r="B872" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="C872" s="5">
+        <v>46093.522916666669</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A873" s="3">
+        <v>85</v>
+      </c>
+      <c r="B873" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="C873" s="5">
+        <v>46093.521527777775</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A874" s="4">
+        <v>86</v>
+      </c>
+      <c r="B874" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="C874" s="5">
+        <v>46093.520833333336</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A875" s="4">
+        <v>87</v>
+      </c>
+      <c r="B875" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="C875" s="5">
+        <v>46093.520138888889</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A876" s="4">
+        <v>88</v>
+      </c>
+      <c r="B876" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="C876" s="5">
+        <v>46093.518750000003</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A877" s="4">
+        <v>89</v>
+      </c>
+      <c r="B877" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="C877" s="5">
+        <v>46093.518750000003</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A878" s="4">
+        <v>90</v>
+      </c>
+      <c r="B878" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="C878" s="5">
+        <v>46093.51666666667</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A879" s="4">
+        <v>91</v>
+      </c>
+      <c r="B879" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C879" s="5">
+        <v>46093.51458333333</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A880" s="4">
+        <v>92</v>
+      </c>
+      <c r="B880" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="C880" s="5">
+        <v>46093.513888888891</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A881" s="4">
+        <v>93</v>
+      </c>
+      <c r="B881" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="C881" s="5">
+        <v>46093.512499999997</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A882" s="4">
+        <v>94</v>
+      </c>
+      <c r="B882" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C882" s="5">
+        <v>46093.511805555558</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A883" s="4">
+        <v>95</v>
+      </c>
+      <c r="B883" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="C883" s="5">
+        <v>46093.511805555558</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A884" s="4">
+        <v>96</v>
+      </c>
+      <c r="B884" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="C884" s="5">
+        <v>46093.511111111111</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A885" s="3">
+        <v>97</v>
+      </c>
+      <c r="B885" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="C885" s="5">
+        <v>46093.510416666664</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A886" s="4">
+        <v>98</v>
+      </c>
+      <c r="B886" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="C886" s="5">
+        <v>46093.510416666664</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A887" s="4">
+        <v>99</v>
+      </c>
+      <c r="B887" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="C887" s="5">
+        <v>46093.509027777778</v>
+      </c>
+    </row>
+    <row r="888" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A888" s="4">
+        <v>100</v>
+      </c>
+      <c r="B888" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="C888" s="5">
+        <v>46093.508333333331</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A889" s="4">
+        <v>101</v>
+      </c>
+      <c r="B889" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="C889" s="5">
+        <v>46093.508333333331</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A890" s="4">
+        <v>102</v>
+      </c>
+      <c r="B890" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="C890" s="5">
+        <v>46093.506249999999</v>
+      </c>
+    </row>
+    <row r="891" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A891" s="4">
+        <v>103</v>
+      </c>
+      <c r="B891" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="C891" s="5">
+        <v>46093.506249999999</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A892" s="4">
+        <v>104</v>
+      </c>
+      <c r="B892" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C892" s="5">
+        <v>46093.505555555559</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A893" s="4">
+        <v>105</v>
+      </c>
+      <c r="B893" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="C893" s="5">
+        <v>46093.504861111112</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A894" s="4">
+        <v>106</v>
+      </c>
+      <c r="B894" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C894" s="5">
+        <v>46093.504166666666</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A895" s="4">
+        <v>107</v>
+      </c>
+      <c r="B895" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="C895" s="5">
+        <v>46093.503472222219</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A896" s="4">
+        <v>108</v>
+      </c>
+      <c r="B896" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="C896" s="5">
+        <v>46093.502083333333</v>
+      </c>
+    </row>
+    <row r="897" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A897" s="3">
+        <v>109</v>
+      </c>
+      <c r="B897" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="C897" s="5">
+        <v>46093.502083333333</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A898" s="4">
+        <v>110</v>
+      </c>
+      <c r="B898" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="C898" s="5">
+        <v>46093.502083333333</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A899" s="4">
+        <v>111</v>
+      </c>
+      <c r="B899" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C899" s="5">
+        <v>46093.501388888886</v>
+      </c>
+    </row>
+    <row r="900" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A900" s="4">
+        <v>112</v>
+      </c>
+      <c r="B900" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C900" s="5">
+        <v>46093.499305555553</v>
+      </c>
+    </row>
+    <row r="901" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A901" s="4">
+        <v>113</v>
+      </c>
+      <c r="B901" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="C901" s="5">
+        <v>46093.498611111114</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A902" s="4">
+        <v>114</v>
+      </c>
+      <c r="B902" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="C902" s="5">
+        <v>46093.497916666667</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A903" s="4">
+        <v>115</v>
+      </c>
+      <c r="B903" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C903" s="5">
+        <v>46093.49722222222</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A904" s="4">
+        <v>116</v>
+      </c>
+      <c r="B904" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="C904" s="5">
+        <v>46093.49722222222</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A905" s="4">
+        <v>117</v>
+      </c>
+      <c r="B905" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="C905" s="5">
+        <v>46093.49722222222</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A906" s="4">
+        <v>118</v>
+      </c>
+      <c r="B906" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="C906" s="5">
+        <v>46093.495833333334</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A907" s="4">
+        <v>119</v>
+      </c>
+      <c r="B907" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="C907" s="5">
+        <v>46093.495138888888</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A908" s="4">
+        <v>120</v>
+      </c>
+      <c r="B908" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="C908" s="5">
+        <v>46093.495138888888</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A909" s="3">
+        <v>121</v>
+      </c>
+      <c r="B909" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="C909" s="5">
+        <v>46093.494444444441</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A910" s="4">
+        <v>122</v>
+      </c>
+      <c r="B910" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="C910" s="5">
+        <v>46093.493750000001</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A911" s="4">
+        <v>123</v>
+      </c>
+      <c r="B911" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="C911" s="5">
+        <v>46093.493750000001</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A912" s="4">
+        <v>124</v>
+      </c>
+      <c r="B912" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="C912" s="5">
+        <v>46093.493750000001</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A913" s="4">
+        <v>125</v>
+      </c>
+      <c r="B913" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="C913" s="5">
+        <v>46093.493055555555</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A914" s="4">
+        <v>126</v>
+      </c>
+      <c r="B914" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="C914" s="5">
+        <v>46093.493055555555</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A915" s="4">
+        <v>127</v>
+      </c>
+      <c r="B915" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="C915" s="5">
+        <v>46093.492361111108</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A916" s="4">
+        <v>128</v>
+      </c>
+      <c r="B916" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="C916" s="5">
+        <v>46093.492361111108</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A917" s="4">
+        <v>129</v>
+      </c>
+      <c r="B917" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="C917" s="5">
+        <v>46093.492361111108</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A918" s="4">
+        <v>130</v>
+      </c>
+      <c r="B918" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="C918" s="5">
+        <v>46093.491666666669</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A919" s="4">
+        <v>131</v>
+      </c>
+      <c r="B919" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C919" s="5">
+        <v>46093.490972222222</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A920" s="4">
+        <v>132</v>
+      </c>
+      <c r="B920" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="C920" s="5">
+        <v>46093.490972222222</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A921" s="3">
+        <v>133</v>
+      </c>
+      <c r="B921" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="C921" s="5">
+        <v>46093.490277777775</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A922" s="4">
+        <v>134</v>
+      </c>
+      <c r="B922" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="C922" s="5">
+        <v>46093.489583333336</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A923" s="4">
+        <v>135</v>
+      </c>
+      <c r="B923" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="C923" s="5">
+        <v>46093.489583333336</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A924" s="4">
+        <v>136</v>
+      </c>
+      <c r="B924" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="C924" s="5">
+        <v>46093.488888888889</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A925" s="4">
+        <v>137</v>
+      </c>
+      <c r="B925" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="C925" s="5">
+        <v>46093.487500000003</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A926" s="4">
+        <v>138</v>
+      </c>
+      <c r="B926" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="C926" s="5">
+        <v>46093.486805555556</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A927" s="4">
+        <v>139</v>
+      </c>
+      <c r="B927" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="C927" s="5">
+        <v>46093.486111111109</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A928" s="4">
+        <v>140</v>
+      </c>
+      <c r="B928" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="C928" s="5">
+        <v>46093.486111111109</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A929" s="4">
+        <v>141</v>
+      </c>
+      <c r="B929" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C929" s="5">
+        <v>46093.48541666667</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A930" s="4">
+        <v>142</v>
+      </c>
+      <c r="B930" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C930" s="5">
+        <v>46093.484722222223</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A931" s="4">
+        <v>143</v>
+      </c>
+      <c r="B931" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="C931" s="5">
+        <v>46093.484027777777</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A932" s="4">
+        <v>144</v>
+      </c>
+      <c r="B932" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="C932" s="5">
+        <v>46093.484027777777</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A933" s="3">
+        <v>145</v>
+      </c>
+      <c r="B933" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="C933" s="5">
+        <v>46093.482638888891</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A934" s="4">
+        <v>146</v>
+      </c>
+      <c r="B934" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="C934" s="5">
+        <v>46093.481944444444</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A935" s="4">
+        <v>147</v>
+      </c>
+      <c r="B935" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="C935" s="5">
+        <v>46093.481944444444</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A936" s="4">
+        <v>148</v>
+      </c>
+      <c r="B936" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="C936" s="5">
+        <v>46093.479861111111</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A937" s="4">
+        <v>149</v>
+      </c>
+      <c r="B937" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="C937" s="5">
+        <v>46093.479166666664</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A938" s="4">
+        <v>150</v>
+      </c>
+      <c r="B938" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="C938" s="5">
+        <v>46093.479166666664</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A939" s="4">
+        <v>151</v>
+      </c>
+      <c r="B939" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="C939" s="5">
+        <v>46093.477777777778</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A940" s="4">
+        <v>152</v>
+      </c>
+      <c r="B940" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="C940" s="5">
+        <v>46093.477777777778</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A941" s="4">
+        <v>153</v>
+      </c>
+      <c r="B941" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="C941" s="5">
+        <v>46093.477083333331</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A942" s="4">
+        <v>154</v>
+      </c>
+      <c r="B942" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="C942" s="5">
+        <v>46093.477083333331</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A943" s="4">
+        <v>155</v>
+      </c>
+      <c r="B943" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="C943" s="5">
+        <v>46093.477083333331</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A944" s="4">
+        <v>156</v>
+      </c>
+      <c r="B944" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="C944" s="5">
+        <v>46093.477083333331</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A945" s="3">
+        <v>157</v>
+      </c>
+      <c r="B945" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="C945" s="5">
+        <v>46093.476388888892</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A946" s="4">
+        <v>158</v>
+      </c>
+      <c r="B946" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="C946" s="5">
+        <v>46093.474999999999</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A947" s="4">
+        <v>159</v>
+      </c>
+      <c r="B947" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="C947" s="5">
+        <v>46093.474305555559</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A948" s="4">
+        <v>160</v>
+      </c>
+      <c r="B948" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="C948" s="5">
+        <v>46093.474305555559</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A949" s="4">
+        <v>161</v>
+      </c>
+      <c r="B949" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="C949" s="5">
+        <v>46093.473611111112</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A950" s="4">
+        <v>162</v>
+      </c>
+      <c r="B950" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="C950" s="5">
+        <v>46093.47152777778</v>
+      </c>
+    </row>
+    <row r="951" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A951" s="4">
+        <v>163</v>
+      </c>
+      <c r="B951" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="C951" s="5">
+        <v>46093.470833333333</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A952" s="4">
+        <v>164</v>
+      </c>
+      <c r="B952" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="C952" s="5">
+        <v>46093.46875</v>
+      </c>
+    </row>
+    <row r="953" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A953" s="4">
+        <v>165</v>
+      </c>
+      <c r="B953" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="C953" s="5">
+        <v>46093.46597222222</v>
+      </c>
+    </row>
+    <row r="954" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A954" s="4">
+        <v>166</v>
+      </c>
+      <c r="B954" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="C954" s="5">
+        <v>46093.465277777781</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A955" s="4">
+        <v>167</v>
+      </c>
+      <c r="B955" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="C955" s="5">
+        <v>46093.463888888888</v>
+      </c>
+    </row>
+    <row r="956" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A956" s="4">
+        <v>168</v>
+      </c>
+      <c r="B956" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="C956" s="5">
+        <v>46093.463194444441</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A957" s="3">
+        <v>169</v>
+      </c>
+      <c r="B957" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="C957" s="5">
+        <v>46093.462500000001</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A958" s="4">
+        <v>170</v>
+      </c>
+      <c r="B958" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="C958" s="5">
+        <v>46093.461111111108</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A959" s="4">
+        <v>171</v>
+      </c>
+      <c r="B959" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="C959" s="5">
+        <v>46093.461111111108</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A960" s="4">
+        <v>172</v>
+      </c>
+      <c r="B960" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="C960" s="5">
+        <v>46093.461111111108</v>
+      </c>
+    </row>
+    <row r="961" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A961" s="4">
+        <v>173</v>
+      </c>
+      <c r="B961" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="C961" s="5">
+        <v>46093.459027777775</v>
+      </c>
+    </row>
+    <row r="962" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A962" s="4">
+        <v>174</v>
+      </c>
+      <c r="B962" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="C962" s="5">
+        <v>46093.456944444442</v>
+      </c>
+    </row>
+    <row r="963" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A963" s="4">
+        <v>175</v>
+      </c>
+      <c r="B963" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="C963" s="5">
+        <v>46093.456944444442</v>
+      </c>
+    </row>
+    <row r="964" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A964" s="4">
+        <v>176</v>
+      </c>
+      <c r="B964" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="C964" s="5">
+        <v>46093.456250000003</v>
+      </c>
+    </row>
+    <row r="965" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A965" s="4">
+        <v>177</v>
+      </c>
+      <c r="B965" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="C965" s="5">
+        <v>46093.456250000003</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A966" s="4">
+        <v>178</v>
+      </c>
+      <c r="B966" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="C966" s="5">
+        <v>46093.456250000003</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A967" s="4">
+        <v>179</v>
+      </c>
+      <c r="B967" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="C967" s="5">
+        <v>46093.45416666667</v>
+      </c>
+    </row>
+    <row r="968" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A968" s="4">
+        <v>180</v>
+      </c>
+      <c r="B968" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="C968" s="5">
+        <v>46093.453472222223</v>
+      </c>
+    </row>
+    <row r="969" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A969" s="3">
+        <v>181</v>
+      </c>
+      <c r="B969" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="C969" s="5">
+        <v>46093.452777777777</v>
+      </c>
+    </row>
+    <row r="970" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A970" s="4">
+        <v>182</v>
+      </c>
+      <c r="B970" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="C970" s="5">
+        <v>46093.452777777777</v>
+      </c>
+    </row>
+    <row r="971" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A971" s="4">
+        <v>183</v>
+      </c>
+      <c r="B971" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="C971" s="5">
+        <v>46093.452777777777</v>
+      </c>
+    </row>
+    <row r="972" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A972" s="4">
+        <v>184</v>
+      </c>
+      <c r="B972" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="C972" s="5">
+        <v>46093.452777777777</v>
+      </c>
+    </row>
+    <row r="973" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A973" s="4">
+        <v>185</v>
+      </c>
+      <c r="B973" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="C973" s="5">
+        <v>46093.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/numbers.xlsx
+++ b/numbers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nodir\Projects\open-budget-search\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CAC716-B4CB-4779-9F69-75DB3CA82D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9C5CC6-A1EC-453D-B0F0-4B57D4E3DD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0AABE945-EFF0-4E0B-A9BD-4BB876D9C82D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="1153">
   <si>
     <t>**-*14-63-61</t>
   </si>
@@ -2887,14 +2887,621 @@
   </si>
   <si>
     <t>**-*56-66-20</t>
+  </si>
+  <si>
+    <t>**-*71-80-85</t>
+  </si>
+  <si>
+    <t>**-*51-67-61</t>
+  </si>
+  <si>
+    <t>**-*18-60-64</t>
+  </si>
+  <si>
+    <t>**-*92-24-92</t>
+  </si>
+  <si>
+    <t>**-*05-27-03</t>
+  </si>
+  <si>
+    <t>**-*83-04-24</t>
+  </si>
+  <si>
+    <t>**-*83-01-82</t>
+  </si>
+  <si>
+    <t>**-*82-76-79</t>
+  </si>
+  <si>
+    <t>**-*74-35-85</t>
+  </si>
+  <si>
+    <t>**-*51-80-04</t>
+  </si>
+  <si>
+    <t>**-*84-84-18</t>
+  </si>
+  <si>
+    <t>**-*00-71-17</t>
+  </si>
+  <si>
+    <t>**-*70-96-19</t>
+  </si>
+  <si>
+    <t>**-*69-11-23</t>
+  </si>
+  <si>
+    <t>**-*78-91-95</t>
+  </si>
+  <si>
+    <t>**-*89-41-91</t>
+  </si>
+  <si>
+    <t>**-*74-55-66</t>
+  </si>
+  <si>
+    <t>**-*17-76-77</t>
+  </si>
+  <si>
+    <t>**-*71-33-08</t>
+  </si>
+  <si>
+    <t>**-*97-43-33</t>
+  </si>
+  <si>
+    <t>**-*89-60-61</t>
+  </si>
+  <si>
+    <t>**-*74-25-84</t>
+  </si>
+  <si>
+    <t>**-*63-78-99</t>
+  </si>
+  <si>
+    <t>**-*93-13-93</t>
+  </si>
+  <si>
+    <t>**-*81-12-61</t>
+  </si>
+  <si>
+    <t>**-*64-00-79</t>
+  </si>
+  <si>
+    <t>**-*52-86-76</t>
+  </si>
+  <si>
+    <t>**-*22-11-87</t>
+  </si>
+  <si>
+    <t>**-*56-77-02</t>
+  </si>
+  <si>
+    <t>**-*46-84-81</t>
+  </si>
+  <si>
+    <t>**-*27-88-07</t>
+  </si>
+  <si>
+    <t>**-*35-89-88</t>
+  </si>
+  <si>
+    <t>**-*46-66-03</t>
+  </si>
+  <si>
+    <t>**-*15-33-66</t>
+  </si>
+  <si>
+    <t>**-*37-00-63</t>
+  </si>
+  <si>
+    <t>**-*47-78-15</t>
+  </si>
+  <si>
+    <t>**-*82-98-00</t>
+  </si>
+  <si>
+    <t>**-*16-22-09</t>
+  </si>
+  <si>
+    <t>**-*92-51-51</t>
+  </si>
+  <si>
+    <t>**-*04-87-90</t>
+  </si>
+  <si>
+    <t>**-*61-16-25</t>
+  </si>
+  <si>
+    <t>**-*89-00-64</t>
+  </si>
+  <si>
+    <t>**-*11-37-74</t>
+  </si>
+  <si>
+    <t>**-*03-22-28</t>
+  </si>
+  <si>
+    <t>**-*89-92-12</t>
+  </si>
+  <si>
+    <t>**-*23-65-05</t>
+  </si>
+  <si>
+    <t>**-*97-92-20</t>
+  </si>
+  <si>
+    <t>**-*11-70-04</t>
+  </si>
+  <si>
+    <t>**-*27-78-78</t>
+  </si>
+  <si>
+    <t>**-*07-95-90</t>
+  </si>
+  <si>
+    <t>**-*52-09-98</t>
+  </si>
+  <si>
+    <t>**-*39-67-07</t>
+  </si>
+  <si>
+    <t>**-*26-92-29</t>
+  </si>
+  <si>
+    <t>**-*11-88-10</t>
+  </si>
+  <si>
+    <t>**-*29-92-26</t>
+  </si>
+  <si>
+    <t>**-*49-44-35</t>
+  </si>
+  <si>
+    <t>**-*73-99-03</t>
+  </si>
+  <si>
+    <t>**-*53-95-72</t>
+  </si>
+  <si>
+    <t>**-*34-95-02</t>
+  </si>
+  <si>
+    <t>**-*79-25-11</t>
+  </si>
+  <si>
+    <t>**-*16-60-33</t>
+  </si>
+  <si>
+    <t>**-*57-05-91</t>
+  </si>
+  <si>
+    <t>**-*57-26-26</t>
+  </si>
+  <si>
+    <t>**-*53-37-55</t>
+  </si>
+  <si>
+    <t>**-*02-99-59</t>
+  </si>
+  <si>
+    <t>**-*82-92-20</t>
+  </si>
+  <si>
+    <t>**-*73-29-91</t>
+  </si>
+  <si>
+    <t>**-*44-17-47</t>
+  </si>
+  <si>
+    <t>**-*42-27-59</t>
+  </si>
+  <si>
+    <t>**-*60-96-80</t>
+  </si>
+  <si>
+    <t>**-*74-03-23</t>
+  </si>
+  <si>
+    <t>**-*33-29-91</t>
+  </si>
+  <si>
+    <t>**-*17-12-55</t>
+  </si>
+  <si>
+    <t>**-*17-88-11</t>
+  </si>
+  <si>
+    <t>**-*66-20-02</t>
+  </si>
+  <si>
+    <t>**-*99-84-94</t>
+  </si>
+  <si>
+    <t>**-*78-10-69</t>
+  </si>
+  <si>
+    <t>**-*50-52-59</t>
+  </si>
+  <si>
+    <t>**-*99-94-19</t>
+  </si>
+  <si>
+    <t>**-*86-40-29</t>
+  </si>
+  <si>
+    <t>**-*15-60-88</t>
+  </si>
+  <si>
+    <t>**-*70-40-29</t>
+  </si>
+  <si>
+    <t>**-*26-84-08</t>
+  </si>
+  <si>
+    <t>**-*54-39-10</t>
+  </si>
+  <si>
+    <t>**-*05-12-78</t>
+  </si>
+  <si>
+    <t>**-*49-01-41</t>
+  </si>
+  <si>
+    <t>**-*36-24-87</t>
+  </si>
+  <si>
+    <t>**-*72-98-08</t>
+  </si>
+  <si>
+    <t>**-*77-07-99</t>
+  </si>
+  <si>
+    <t>**-*51-08-87</t>
+  </si>
+  <si>
+    <t>**-*77-49-06</t>
+  </si>
+  <si>
+    <t>**-*96-20-18</t>
+  </si>
+  <si>
+    <t>**-*40-75-73</t>
+  </si>
+  <si>
+    <t>**-*44-75-73</t>
+  </si>
+  <si>
+    <t>**-*64-02-91</t>
+  </si>
+  <si>
+    <t>**-*03-79-99</t>
+  </si>
+  <si>
+    <t>**-*32-31-60</t>
+  </si>
+  <si>
+    <t>**-*01-84-88</t>
+  </si>
+  <si>
+    <t>**-*31-56-92</t>
+  </si>
+  <si>
+    <t>**-*02-70-80</t>
+  </si>
+  <si>
+    <t>**-*09-19-83</t>
+  </si>
+  <si>
+    <t>**-*27-11-30</t>
+  </si>
+  <si>
+    <t>**-*33-08-95</t>
+  </si>
+  <si>
+    <t>**-*06-83-97</t>
+  </si>
+  <si>
+    <t>**-*04-14-66</t>
+  </si>
+  <si>
+    <t>**-*56-25-91</t>
+  </si>
+  <si>
+    <t>**-*69-17-76</t>
+  </si>
+  <si>
+    <t>**-*46-73-71</t>
+  </si>
+  <si>
+    <t>**-*16-16-82</t>
+  </si>
+  <si>
+    <t>**-*09-95-07</t>
+  </si>
+  <si>
+    <t>**-*09-61-05</t>
+  </si>
+  <si>
+    <t>**-*74-79-79</t>
+  </si>
+  <si>
+    <t>**-*73-73-15</t>
+  </si>
+  <si>
+    <t>**-*56-62-10</t>
+  </si>
+  <si>
+    <t>**-*50-56-42</t>
+  </si>
+  <si>
+    <t>**-*17-17-11</t>
+  </si>
+  <si>
+    <t>**-*98-01-70</t>
+  </si>
+  <si>
+    <t>**-*80-75-95</t>
+  </si>
+  <si>
+    <t>**-*67-01-83</t>
+  </si>
+  <si>
+    <t>**-*71-04-98</t>
+  </si>
+  <si>
+    <t>**-*43-43-86</t>
+  </si>
+  <si>
+    <t>**-*56-27-85</t>
+  </si>
+  <si>
+    <t>**-*58-11-17</t>
+  </si>
+  <si>
+    <t>**-*70-84-21</t>
+  </si>
+  <si>
+    <t>**-*72-26-07</t>
+  </si>
+  <si>
+    <t>**-*12-76-20</t>
+  </si>
+  <si>
+    <t>**-*14-18-10</t>
+  </si>
+  <si>
+    <t>**-*38-98-00</t>
+  </si>
+  <si>
+    <t>**-*91-65-66</t>
+  </si>
+  <si>
+    <t>**-*08-01-02</t>
+  </si>
+  <si>
+    <t>**-*60-06-91</t>
+  </si>
+  <si>
+    <t>**-*78-58-77</t>
+  </si>
+  <si>
+    <t>**-*96-23-07</t>
+  </si>
+  <si>
+    <t>**-*08-84-72</t>
+  </si>
+  <si>
+    <t>**-*84-90-88</t>
+  </si>
+  <si>
+    <t>**-*86-67-72</t>
+  </si>
+  <si>
+    <t>**-*22-97-79</t>
+  </si>
+  <si>
+    <t>**-*93-94-98</t>
+  </si>
+  <si>
+    <t>**-*22-95-05</t>
+  </si>
+  <si>
+    <t>**-*33-11-14</t>
+  </si>
+  <si>
+    <t>**-*13-44-51</t>
+  </si>
+  <si>
+    <t>**-*76-25-28</t>
+  </si>
+  <si>
+    <t>**-*27-58-84</t>
+  </si>
+  <si>
+    <t>**-*48-08-60</t>
+  </si>
+  <si>
+    <t>**-*80-55-30</t>
+  </si>
+  <si>
+    <t>**-*76-35-81</t>
+  </si>
+  <si>
+    <t>**-*03-36-84</t>
+  </si>
+  <si>
+    <t>**-*24-76-72</t>
+  </si>
+  <si>
+    <t>**-*16-48-47</t>
+  </si>
+  <si>
+    <t>**-*00-13-74</t>
+  </si>
+  <si>
+    <t>**-*42-83-38</t>
+  </si>
+  <si>
+    <t>**-*42-19-54</t>
+  </si>
+  <si>
+    <t>**-*65-20-01</t>
+  </si>
+  <si>
+    <t>**-*00-88-65</t>
+  </si>
+  <si>
+    <t>**-*10-99-93</t>
+  </si>
+  <si>
+    <t>**-*63-47-57</t>
+  </si>
+  <si>
+    <t>**-*00-28-29</t>
+  </si>
+  <si>
+    <t>**-*07-69-71</t>
+  </si>
+  <si>
+    <t>**-*76-19-59</t>
+  </si>
+  <si>
+    <t>**-*28-25-98</t>
+  </si>
+  <si>
+    <t>**-*82-95-07</t>
+  </si>
+  <si>
+    <t>**-*78-06-77</t>
+  </si>
+  <si>
+    <t>**-*01-93-00</t>
+  </si>
+  <si>
+    <t>**-*52-88-65</t>
+  </si>
+  <si>
+    <t>**-*06-26-50</t>
+  </si>
+  <si>
+    <t>**-*25-25-36</t>
+  </si>
+  <si>
+    <t>**-*52-37-20</t>
+  </si>
+  <si>
+    <t>**-*95-21-60</t>
+  </si>
+  <si>
+    <t>**-*79-58-90</t>
+  </si>
+  <si>
+    <t>**-*71-21-92</t>
+  </si>
+  <si>
+    <t>**-*94-21-01</t>
+  </si>
+  <si>
+    <t>**-*43-11-76</t>
+  </si>
+  <si>
+    <t>**-*89-93-77</t>
+  </si>
+  <si>
+    <t>**-*12-04-94</t>
+  </si>
+  <si>
+    <t>**-*42-46-81</t>
+  </si>
+  <si>
+    <t>**-*03-88-37</t>
+  </si>
+  <si>
+    <t>**-*56-57-75</t>
+  </si>
+  <si>
+    <t>**-*73-24-88</t>
+  </si>
+  <si>
+    <t>**-*64-77-81</t>
+  </si>
+  <si>
+    <t>**-*93-88-31</t>
+  </si>
+  <si>
+    <t>**-*38-42-82</t>
+  </si>
+  <si>
+    <t>**-*94-31-31</t>
+  </si>
+  <si>
+    <t>**-*78-00-68</t>
+  </si>
+  <si>
+    <t>**-*61-72-09</t>
+  </si>
+  <si>
+    <t>**-*32-36-41</t>
+  </si>
+  <si>
+    <t>**-*88-41-93</t>
+  </si>
+  <si>
+    <t>**-*06-38-39</t>
+  </si>
+  <si>
+    <t>**-*00-68-98</t>
+  </si>
+  <si>
+    <t>**-*11-40-37</t>
+  </si>
+  <si>
+    <t>**-*12-89-69</t>
+  </si>
+  <si>
+    <t>**-*69-55-60</t>
+  </si>
+  <si>
+    <t>**-*44-06-33</t>
+  </si>
+  <si>
+    <t>**-*70-08-33</t>
+  </si>
+  <si>
+    <t>**-*59-91-99</t>
+  </si>
+  <si>
+    <t>**-*47-97-00</t>
+  </si>
+  <si>
+    <t>**-*40-70-03</t>
+  </si>
+  <si>
+    <t>**-*93-47-77</t>
+  </si>
+  <si>
+    <t>**-*53-09-21</t>
+  </si>
+  <si>
+    <t>**-*14-05-16</t>
+  </si>
+  <si>
+    <t>**-*03-53-83</t>
+  </si>
+  <si>
+    <t>**-*66-94-91</t>
+  </si>
+  <si>
+    <t>**-*94-01-81</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="171" formatCode="dd\-mm\-yyyy\ hh:mm"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -2984,7 +3591,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3012,6 +3619,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3328,14 +3938,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA66EC08-8D26-46AA-A6AA-1D6A0B4C73D5}">
-  <dimension ref="A7:C973"/>
+  <dimension ref="A7:H973"/>
   <sheetFormatPr defaultRowHeight="21" thickBottom="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25.28515625" customWidth="1"/>
     <col min="3" max="3" width="26" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.28515625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3345,8 +3958,17 @@
       <c r="C7" s="5">
         <v>46093.425000000003</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="H7" s="10">
+        <v>46094.332638888889</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>2</v>
       </c>
@@ -3356,8 +3978,17 @@
       <c r="C8" s="5">
         <v>46093.421527777777</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="4">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="H8" s="10">
+        <v>46094.331944444442</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>3</v>
       </c>
@@ -3367,8 +3998,17 @@
       <c r="C9" s="5">
         <v>46093.418749999997</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F9" s="4">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="H9" s="10">
+        <v>46094.331944444442</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>4</v>
       </c>
@@ -3378,8 +4018,17 @@
       <c r="C10" s="5">
         <v>46093.415972222225</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F10" s="4">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="H10" s="10">
+        <v>46094.322222222225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>5</v>
       </c>
@@ -3389,8 +4038,17 @@
       <c r="C11" s="5">
         <v>46093.415277777778</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F11" s="4">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="H11" s="10">
+        <v>46094.321527777778</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>6</v>
       </c>
@@ -3400,8 +4058,17 @@
       <c r="C12" s="5">
         <v>46093.414583333331</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F12" s="4">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="H12" s="10">
+        <v>46094.320833333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>7</v>
       </c>
@@ -3411,8 +4078,17 @@
       <c r="C13" s="5">
         <v>46093.414583333331</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F13" s="4">
+        <v>7</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="H13" s="10">
+        <v>46094.320138888892</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>8</v>
       </c>
@@ -3422,8 +4098,17 @@
       <c r="C14" s="5">
         <v>46093.413888888892</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F14" s="4">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="H14" s="10">
+        <v>46094.308333333334</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>9</v>
       </c>
@@ -3433,8 +4118,17 @@
       <c r="C15" s="5">
         <v>46093.413888888892</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F15" s="4">
+        <v>9</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="H15" s="10">
+        <v>46094.306944444441</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>10</v>
       </c>
@@ -3444,8 +4138,17 @@
       <c r="C16" s="5">
         <v>46093.411805555559</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F16" s="4">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="H16" s="10">
+        <v>46094.298611111109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>11</v>
       </c>
@@ -3455,8 +4158,17 @@
       <c r="C17" s="5">
         <v>46093.411111111112</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F17" s="4">
+        <v>11</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="H17" s="10">
+        <v>46094.290277777778</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>12</v>
       </c>
@@ -3466,8 +4178,17 @@
       <c r="C18" s="5">
         <v>46093.411111111112</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F18" s="4">
+        <v>12</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="H18" s="10">
+        <v>46094.284722222219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>13</v>
       </c>
@@ -3477,8 +4198,17 @@
       <c r="C19" s="5">
         <v>46093.409722222219</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F19" s="3">
+        <v>13</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="H19" s="10">
+        <v>46094.272916666669</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>14</v>
       </c>
@@ -3488,8 +4218,17 @@
       <c r="C20" s="5">
         <v>46093.40902777778</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F20" s="4">
+        <v>14</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="H20" s="10">
+        <v>46094.267361111109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>15</v>
       </c>
@@ -3499,8 +4238,17 @@
       <c r="C21" s="5">
         <v>46093.40902777778</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F21" s="4">
+        <v>15</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="H21" s="10">
+        <v>46094.265972222223</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>16</v>
       </c>
@@ -3510,8 +4258,17 @@
       <c r="C22" s="5">
         <v>46093.408333333333</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F22" s="4">
+        <v>16</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="H22" s="10">
+        <v>46094.255555555559</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>17</v>
       </c>
@@ -3521,8 +4278,17 @@
       <c r="C23" s="5">
         <v>46093.406944444447</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F23" s="4">
+        <v>17</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="H23" s="10">
+        <v>46094.238888888889</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>18</v>
       </c>
@@ -3532,8 +4298,17 @@
       <c r="C24" s="5">
         <v>46093.406944444447</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F24" s="4">
+        <v>18</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="H24" s="10">
+        <v>46094.231249999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>1</v>
       </c>
@@ -3543,8 +4318,17 @@
       <c r="C25" s="5">
         <v>46093.40347222222</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F25" s="4">
+        <v>19</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="H25" s="10">
+        <v>46094.224999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>2</v>
       </c>
@@ -3554,8 +4338,17 @@
       <c r="C26" s="5">
         <v>46093.402083333334</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F26" s="4">
+        <v>20</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="H26" s="10">
+        <v>46094.220138888886</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>3</v>
       </c>
@@ -3565,8 +4358,17 @@
       <c r="C27" s="5">
         <v>46093.401388888888</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F27" s="4">
+        <v>21</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="H27" s="10">
+        <v>46094.216666666667</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>4</v>
       </c>
@@ -3576,8 +4378,17 @@
       <c r="C28" s="5">
         <v>46093.401388888888</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F28" s="4">
+        <v>22</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="H28" s="10">
+        <v>46094.198611111111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>5</v>
       </c>
@@ -3587,8 +4398,17 @@
       <c r="C29" s="5">
         <v>46093.400694444441</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F29" s="4">
+        <v>23</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="H29" s="10">
+        <v>46094.197916666664</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>6</v>
       </c>
@@ -3598,8 +4418,17 @@
       <c r="C30" s="5">
         <v>46093.4</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F30" s="4">
+        <v>24</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="H30" s="10">
+        <v>46094.1875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>7</v>
       </c>
@@ -3609,8 +4438,17 @@
       <c r="C31" s="5">
         <v>46093.399305555555</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="3">
+        <v>25</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="H31" s="10">
+        <v>46094.168055555558</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>8</v>
       </c>
@@ -3620,8 +4458,17 @@
       <c r="C32" s="5">
         <v>46093.398611111108</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F32" s="4">
+        <v>26</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="H32" s="10">
+        <v>46094.163194444445</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>9</v>
       </c>
@@ -3631,8 +4478,17 @@
       <c r="C33" s="5">
         <v>46093.395138888889</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F33" s="4">
+        <v>27</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="H33" s="10">
+        <v>46094.150694444441</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>10</v>
       </c>
@@ -3642,8 +4498,17 @@
       <c r="C34" s="5">
         <v>46093.395138888889</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F34" s="4">
+        <v>28</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="H34" s="10">
+        <v>46094.15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>11</v>
       </c>
@@ -3653,8 +4518,17 @@
       <c r="C35" s="5">
         <v>46093.394444444442</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F35" s="4">
+        <v>29</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="H35" s="10">
+        <v>46094.15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>12</v>
       </c>
@@ -3664,8 +4538,17 @@
       <c r="C36" s="5">
         <v>46093.394444444442</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F36" s="4">
+        <v>30</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="H36" s="10">
+        <v>46094.134027777778</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>13</v>
       </c>
@@ -3675,8 +4558,17 @@
       <c r="C37" s="5">
         <v>46093.388194444444</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F37" s="4">
+        <v>31</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="H37" s="10">
+        <v>46094.132638888892</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>14</v>
       </c>
@@ -3686,8 +4578,17 @@
       <c r="C38" s="5">
         <v>46093.388194444444</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F38" s="4">
+        <v>32</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="H38" s="10">
+        <v>46094.109027777777</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>15</v>
       </c>
@@ -3697,8 +4598,17 @@
       <c r="C39" s="5">
         <v>46093.385416666664</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F39" s="4">
+        <v>33</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="H39" s="10">
+        <v>46094.081944444442</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>16</v>
       </c>
@@ -3708,8 +4618,17 @@
       <c r="C40" s="5">
         <v>46093.384027777778</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F40" s="4">
+        <v>34</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="H40" s="10">
+        <v>46094.081250000003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>17</v>
       </c>
@@ -3719,8 +4638,17 @@
       <c r="C41" s="5">
         <v>46093.383333333331</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F41" s="4">
+        <v>35</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="H41" s="10">
+        <v>46094.071527777778</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>18</v>
       </c>
@@ -3730,8 +4658,17 @@
       <c r="C42" s="5">
         <v>46093.381249999999</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F42" s="4">
+        <v>36</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="H42" s="10">
+        <v>46094.038194444445</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>19</v>
       </c>
@@ -3741,8 +4678,17 @@
       <c r="C43" s="5">
         <v>46093.377083333333</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F43" s="3">
+        <v>37</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="H43" s="10">
+        <v>46094.003472222219</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>20</v>
       </c>
@@ -3752,8 +4698,17 @@
       <c r="C44" s="5">
         <v>46093.370833333334</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F44" s="4">
+        <v>38</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="H44" s="10">
+        <v>46093.994444444441</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>21</v>
       </c>
@@ -3763,8 +4718,17 @@
       <c r="C45" s="5">
         <v>46093.351388888892</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F45" s="4">
+        <v>39</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="H45" s="10">
+        <v>46093.988194444442</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>22</v>
       </c>
@@ -3774,8 +4738,17 @@
       <c r="C46" s="5">
         <v>46093.336805555555</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F46" s="4">
+        <v>40</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="H46" s="10">
+        <v>46093.98541666667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>23</v>
       </c>
@@ -3785,8 +4758,17 @@
       <c r="C47" s="5">
         <v>46093.306944444441</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F47" s="4">
+        <v>41</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="H47" s="10">
+        <v>46093.984027777777</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>24</v>
       </c>
@@ -3796,8 +4778,17 @@
       <c r="C48" s="5">
         <v>46093.296527777777</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F48" s="4">
+        <v>42</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="H48" s="10">
+        <v>46093.976388888892</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>25</v>
       </c>
@@ -3807,8 +4798,17 @@
       <c r="C49" s="5">
         <v>46093.306944444441</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F49" s="4">
+        <v>43</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="H49" s="10">
+        <v>46093.973611111112</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>26</v>
       </c>
@@ -3818,8 +4818,17 @@
       <c r="C50" s="5">
         <v>46093.296527777777</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F50" s="4">
+        <v>44</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="H50" s="10">
+        <v>46093.972916666666</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>27</v>
       </c>
@@ -3829,8 +4838,17 @@
       <c r="C51" s="5">
         <v>46093.236805555556</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F51" s="4">
+        <v>45</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="H51" s="10">
+        <v>46093.961805555555</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>28</v>
       </c>
@@ -3840,8 +4858,17 @@
       <c r="C52" s="5">
         <v>46092.972916666666</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F52" s="4">
+        <v>46</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="H52" s="10">
+        <v>46093.961111111108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>29</v>
       </c>
@@ -3851,8 +4878,17 @@
       <c r="C53" s="5">
         <v>46092.944444444445</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F53" s="4">
+        <v>47</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="H53" s="10">
+        <v>46093.959722222222</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>30</v>
       </c>
@@ -3862,8 +4898,17 @@
       <c r="C54" s="5">
         <v>46092.943055555559</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F54" s="4">
+        <v>48</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="H54" s="10">
+        <v>46093.957638888889</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>31</v>
       </c>
@@ -3873,8 +4918,17 @@
       <c r="C55" s="5">
         <v>46092.9375</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F55" s="3">
+        <v>49</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="H55" s="10">
+        <v>46093.956250000003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>32</v>
       </c>
@@ -3884,8 +4938,17 @@
       <c r="C56" s="5">
         <v>46092.934027777781</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F56" s="4">
+        <v>50</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H56" s="10">
+        <v>46093.954861111109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>33</v>
       </c>
@@ -3895,8 +4958,17 @@
       <c r="C57" s="5">
         <v>46092.928472222222</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F57" s="4">
+        <v>51</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H57" s="10">
+        <v>46093.950694444444</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>34</v>
       </c>
@@ -3906,8 +4978,17 @@
       <c r="C58" s="5">
         <v>46092.927083333336</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F58" s="4">
+        <v>52</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H58" s="10">
+        <v>46093.949305555558</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>35</v>
       </c>
@@ -3917,8 +4998,17 @@
       <c r="C59" s="5">
         <v>46092.925000000003</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F59" s="4">
+        <v>53</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H59" s="10">
+        <v>46093.945833333331</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>36</v>
       </c>
@@ -3928,8 +5018,17 @@
       <c r="C60" s="5">
         <v>46092.924305555556</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F60" s="4">
+        <v>54</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H60" s="10">
+        <v>46093.938888888886</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>37</v>
       </c>
@@ -3939,8 +5038,17 @@
       <c r="C61" s="5">
         <v>46092.923611111109</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F61" s="4">
+        <v>55</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H61" s="10">
+        <v>46093.921527777777</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>38</v>
       </c>
@@ -3950,8 +5058,17 @@
       <c r="C62" s="5">
         <v>46092.921527777777</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F62" s="4">
+        <v>56</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H62" s="10">
+        <v>46093.92083333333</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>39</v>
       </c>
@@ -3961,8 +5078,17 @@
       <c r="C63" s="5">
         <v>46092.921527777777</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F63" s="4">
+        <v>57</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H63" s="10">
+        <v>46093.920138888891</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>40</v>
       </c>
@@ -3972,8 +5098,17 @@
       <c r="C64" s="5">
         <v>46092.919444444444</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F64" s="4">
+        <v>58</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H64" s="10">
+        <v>46093.919444444444</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>41</v>
       </c>
@@ -3983,8 +5118,17 @@
       <c r="C65" s="5">
         <v>46092.918055555558</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F65" s="4">
+        <v>59</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H65" s="10">
+        <v>46093.915972222225</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>42</v>
       </c>
@@ -3994,8 +5138,17 @@
       <c r="C66" s="5">
         <v>46092.916666666664</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F66" s="4">
+        <v>60</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H66" s="10">
+        <v>46093.912499999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>43</v>
       </c>
@@ -4005,8 +5158,17 @@
       <c r="C67" s="5">
         <v>46092.915972222225</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F67" s="3">
+        <v>61</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H67" s="10">
+        <v>46093.910416666666</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>44</v>
       </c>
@@ -4016,8 +5178,17 @@
       <c r="C68" s="5">
         <v>46092.910416666666</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F68" s="4">
+        <v>62</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H68" s="10">
+        <v>46093.90902777778</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>45</v>
       </c>
@@ -4027,8 +5198,17 @@
       <c r="C69" s="5">
         <v>46092.909722222219</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F69" s="4">
+        <v>63</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H69" s="10">
+        <v>46093.90625</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>46</v>
       </c>
@@ -4038,8 +5218,17 @@
       <c r="C70" s="5">
         <v>46092.90902777778</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F70" s="4">
+        <v>64</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H70" s="10">
+        <v>46093.90625</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>47</v>
       </c>
@@ -4049,8 +5238,17 @@
       <c r="C71" s="5">
         <v>46092.907638888886</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F71" s="4">
+        <v>65</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H71" s="10">
+        <v>46093.899305555555</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>48</v>
       </c>
@@ -4060,8 +5258,17 @@
       <c r="C72" s="5">
         <v>46092.905555555553</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F72" s="4">
+        <v>66</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H72" s="10">
+        <v>46093.897222222222</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>49</v>
       </c>
@@ -4071,8 +5278,17 @@
       <c r="C73" s="5">
         <v>46092.904861111114</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F73" s="4">
+        <v>67</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="H73" s="10">
+        <v>46093.897222222222</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>50</v>
       </c>
@@ -4082,8 +5298,17 @@
       <c r="C74" s="5">
         <v>46092.902777777781</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F74" s="4">
+        <v>68</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H74" s="10">
+        <v>46093.895138888889</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>51</v>
       </c>
@@ -4093,8 +5318,17 @@
       <c r="C75" s="5">
         <v>46092.901388888888</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F75" s="4">
+        <v>69</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H75" s="10">
+        <v>46093.893750000003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>52</v>
       </c>
@@ -4104,8 +5338,17 @@
       <c r="C76" s="5">
         <v>46092.897222222222</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F76" s="4">
+        <v>70</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H76" s="10">
+        <v>46093.892361111109</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>53</v>
       </c>
@@ -4115,8 +5358,17 @@
       <c r="C77" s="5">
         <v>46092.893750000003</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F77" s="4">
+        <v>71</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H77" s="10">
+        <v>46093.89166666667</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>54</v>
       </c>
@@ -4126,8 +5378,17 @@
       <c r="C78" s="5">
         <v>46092.892361111109</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F78" s="4">
+        <v>72</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H78" s="10">
+        <v>46093.890972222223</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>55</v>
       </c>
@@ -4137,8 +5398,17 @@
       <c r="C79" s="5">
         <v>46092.890972222223</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F79" s="3">
+        <v>73</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H79" s="10">
+        <v>46093.890972222223</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>56</v>
       </c>
@@ -4148,8 +5418,17 @@
       <c r="C80" s="5">
         <v>46092.890972222223</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F80" s="4">
+        <v>74</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H80" s="10">
+        <v>46093.890277777777</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>57</v>
       </c>
@@ -4159,8 +5438,17 @@
       <c r="C81" s="5">
         <v>46092.890277777777</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F81" s="4">
+        <v>75</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H81" s="10">
+        <v>46093.888194444444</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>58</v>
       </c>
@@ -4170,8 +5458,17 @@
       <c r="C82" s="5">
         <v>46092.888194444444</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F82" s="4">
+        <v>76</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H82" s="10">
+        <v>46093.886111111111</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>59</v>
       </c>
@@ -4181,8 +5478,17 @@
       <c r="C83" s="5">
         <v>46092.888194444444</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F83" s="4">
+        <v>77</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H83" s="10">
+        <v>46093.884722222225</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>60</v>
       </c>
@@ -4192,8 +5498,17 @@
       <c r="C84" s="5">
         <v>46092.886111111111</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F84" s="4">
+        <v>78</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H84" s="10">
+        <v>46093.884722222225</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>61</v>
       </c>
@@ -4203,8 +5518,17 @@
       <c r="C85" s="5">
         <v>46092.886111111111</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F85" s="4">
+        <v>79</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H85" s="10">
+        <v>46093.883333333331</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>62</v>
       </c>
@@ -4214,8 +5538,17 @@
       <c r="C86" s="5">
         <v>46092.884027777778</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F86" s="4">
+        <v>80</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H86" s="10">
+        <v>46093.881944444445</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>63</v>
       </c>
@@ -4225,8 +5558,17 @@
       <c r="C87" s="5">
         <v>46092.883333333331</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F87" s="4">
+        <v>81</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H87" s="10">
+        <v>46093.881249999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>64</v>
       </c>
@@ -4236,8 +5578,17 @@
       <c r="C88" s="5">
         <v>46092.882638888892</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F88" s="4">
+        <v>82</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H88" s="10">
+        <v>46093.880555555559</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>65</v>
       </c>
@@ -4247,8 +5598,17 @@
       <c r="C89" s="5">
         <v>46092.880555555559</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F89" s="4">
+        <v>83</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H89" s="10">
+        <v>46093.878472222219</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>66</v>
       </c>
@@ -4258,8 +5618,17 @@
       <c r="C90" s="5">
         <v>46092.879861111112</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F90" s="4">
+        <v>84</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H90" s="10">
+        <v>46093.87777777778</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>67</v>
       </c>
@@ -4269,8 +5638,17 @@
       <c r="C91" s="5">
         <v>46092.879861111112</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F91" s="3">
+        <v>85</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H91" s="10">
+        <v>46093.877083333333</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>68</v>
       </c>
@@ -4280,8 +5658,17 @@
       <c r="C92" s="5">
         <v>46092.879166666666</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F92" s="4">
+        <v>86</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H92" s="10">
+        <v>46093.873611111114</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>69</v>
       </c>
@@ -4291,8 +5678,17 @@
       <c r="C93" s="5">
         <v>46092.87777777778</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F93" s="4">
+        <v>87</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H93" s="10">
+        <v>46093.872916666667</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>70</v>
       </c>
@@ -4302,8 +5698,17 @@
       <c r="C94" s="5">
         <v>46092.875</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F94" s="4">
+        <v>88</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H94" s="10">
+        <v>46093.867361111108</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>71</v>
       </c>
@@ -4313,8 +5718,17 @@
       <c r="C95" s="5">
         <v>46092.874305555553</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F95" s="4">
+        <v>89</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H95" s="10">
+        <v>46093.863888888889</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>72</v>
       </c>
@@ -4324,8 +5738,17 @@
       <c r="C96" s="5">
         <v>46092.872916666667</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F96" s="4">
+        <v>90</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H96" s="10">
+        <v>46093.859722222223</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>73</v>
       </c>
@@ -4335,8 +5758,17 @@
       <c r="C97" s="5">
         <v>46092.87222222222</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F97" s="4">
+        <v>91</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H97" s="10">
+        <v>46093.855555555558</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>74</v>
       </c>
@@ -4346,8 +5778,17 @@
       <c r="C98" s="5">
         <v>46092.87222222222</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F98" s="4">
+        <v>92</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H98" s="10">
+        <v>46093.852083333331</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>75</v>
       </c>
@@ -4357,8 +5798,17 @@
       <c r="C99" s="5">
         <v>46092.871527777781</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F99" s="4">
+        <v>93</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H99" s="10">
+        <v>46093.828472222223</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>76</v>
       </c>
@@ -4368,8 +5818,17 @@
       <c r="C100" s="5">
         <v>46092.871527777781</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F100" s="4">
+        <v>94</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H100" s="10">
+        <v>46093.826388888891</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>77</v>
       </c>
@@ -4379,8 +5838,17 @@
       <c r="C101" s="5">
         <v>46092.867361111108</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F101" s="4">
+        <v>95</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H101" s="10">
+        <v>46093.824999999997</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>78</v>
       </c>
@@ -4390,8 +5858,17 @@
       <c r="C102" s="5">
         <v>46092.866666666669</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F102" s="4">
+        <v>96</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H102" s="10">
+        <v>46093.818055555559</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>79</v>
       </c>
@@ -4401,8 +5878,17 @@
       <c r="C103" s="5">
         <v>46092.866666666669</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F103" s="3">
+        <v>97</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H103" s="10">
+        <v>46093.814583333333</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>80</v>
       </c>
@@ -4412,8 +5898,17 @@
       <c r="C104" s="5">
         <v>46092.862500000003</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F104" s="4">
+        <v>98</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H104" s="10">
+        <v>46093.8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>81</v>
       </c>
@@ -4423,8 +5918,17 @@
       <c r="C105" s="5">
         <v>46092.861805555556</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F105" s="4">
+        <v>99</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H105" s="10">
+        <v>46093.769444444442</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>82</v>
       </c>
@@ -4434,8 +5938,17 @@
       <c r="C106" s="5">
         <v>46092.861111111109</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F106" s="4">
+        <v>100</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H106" s="10">
+        <v>46093.768055555556</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>83</v>
       </c>
@@ -4445,8 +5958,17 @@
       <c r="C107" s="5">
         <v>46092.859722222223</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F107" s="4">
+        <v>101</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H107" s="10">
+        <v>46093.759722222225</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>84</v>
       </c>
@@ -4456,8 +5978,17 @@
       <c r="C108" s="5">
         <v>46092.859027777777</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F108" s="4">
+        <v>102</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H108" s="10">
+        <v>46093.758333333331</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>85</v>
       </c>
@@ -4467,8 +5998,17 @@
       <c r="C109" s="5">
         <v>46092.85833333333</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F109" s="4">
+        <v>103</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H109" s="10">
+        <v>46093.754166666666</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>86</v>
       </c>
@@ -4478,8 +6018,17 @@
       <c r="C110" s="5">
         <v>46092.857638888891</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F110" s="4">
+        <v>104</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H110" s="10">
+        <v>46093.75</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>87</v>
       </c>
@@ -4489,8 +6038,17 @@
       <c r="C111" s="5">
         <v>46092.856944444444</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F111" s="4">
+        <v>105</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H111" s="10">
+        <v>46093.744444444441</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>88</v>
       </c>
@@ -4500,8 +6058,17 @@
       <c r="C112" s="5">
         <v>46092.856944444444</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F112" s="4">
+        <v>106</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H112" s="10">
+        <v>46093.742361111108</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>89</v>
       </c>
@@ -4511,8 +6078,17 @@
       <c r="C113" s="5">
         <v>46092.854166666664</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F113" s="4">
+        <v>107</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H113" s="10">
+        <v>46093.740972222222</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>90</v>
       </c>
@@ -4522,8 +6098,17 @@
       <c r="C114" s="5">
         <v>46092.853472222225</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F114" s="4">
+        <v>108</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H114" s="10">
+        <v>46093.740277777775</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>91</v>
       </c>
@@ -4533,8 +6118,17 @@
       <c r="C115" s="5">
         <v>46092.852777777778</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F115" s="3">
+        <v>109</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H115" s="10">
+        <v>46093.740277777775</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>92</v>
       </c>
@@ -4544,8 +6138,17 @@
       <c r="C116" s="5">
         <v>46092.851388888892</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F116" s="4">
+        <v>110</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H116" s="10">
+        <v>46093.738888888889</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>93</v>
       </c>
@@ -4555,8 +6158,17 @@
       <c r="C117" s="5">
         <v>46092.851388888892</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F117" s="4">
+        <v>111</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H117" s="10">
+        <v>46093.738888888889</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>94</v>
       </c>
@@ -4566,8 +6178,17 @@
       <c r="C118" s="5">
         <v>46092.849305555559</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F118" s="4">
+        <v>112</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H118" s="10">
+        <v>46093.731944444444</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>95</v>
       </c>
@@ -4577,8 +6198,17 @@
       <c r="C119" s="5">
         <v>46092.84652777778</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F119" s="4">
+        <v>113</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H119" s="10">
+        <v>46093.731944444444</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>96</v>
       </c>
@@ -4588,8 +6218,17 @@
       <c r="C120" s="5">
         <v>46092.845138888886</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F120" s="4">
+        <v>114</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H120" s="10">
+        <v>46093.731249999997</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>97</v>
       </c>
@@ -4599,8 +6238,17 @@
       <c r="C121" s="5">
         <v>46092.842361111114</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F121" s="4">
+        <v>115</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H121" s="10">
+        <v>46093.730555555558</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>98</v>
       </c>
@@ -4610,8 +6258,17 @@
       <c r="C122" s="5">
         <v>46092.841666666667</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F122" s="4">
+        <v>116</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H122" s="10">
+        <v>46093.728472222225</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>99</v>
       </c>
@@ -4621,8 +6278,17 @@
       <c r="C123" s="5">
         <v>46092.838888888888</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F123" s="4">
+        <v>117</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H123" s="10">
+        <v>46093.727777777778</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>100</v>
       </c>
@@ -4632,8 +6298,17 @@
       <c r="C124" s="5">
         <v>46092.838888888888</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F124" s="4">
+        <v>118</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H124" s="10">
+        <v>46093.727083333331</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>101</v>
       </c>
@@ -4643,8 +6318,17 @@
       <c r="C125" s="5">
         <v>46092.835416666669</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F125" s="4">
+        <v>119</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H125" s="10">
+        <v>46093.726388888892</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>102</v>
       </c>
@@ -4654,8 +6338,17 @@
       <c r="C126" s="5">
         <v>46092.833333333336</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F126" s="4">
+        <v>120</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H126" s="10">
+        <v>46093.724305555559</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>103</v>
       </c>
@@ -4665,8 +6358,17 @@
       <c r="C127" s="5">
         <v>46092.831944444442</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F127" s="3">
+        <v>121</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H127" s="10">
+        <v>46093.723611111112</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>104</v>
       </c>
@@ -4676,8 +6378,17 @@
       <c r="C128" s="5">
         <v>46092.830555555556</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F128" s="4">
+        <v>122</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H128" s="10">
+        <v>46093.723611111112</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>105</v>
       </c>
@@ -4687,8 +6398,17 @@
       <c r="C129" s="5">
         <v>46092.829861111109</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F129" s="4">
+        <v>123</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="H129" s="10">
+        <v>46093.722222222219</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>106</v>
       </c>
@@ -4698,8 +6418,17 @@
       <c r="C130" s="5">
         <v>46092.827777777777</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F130" s="4">
+        <v>124</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H130" s="10">
+        <v>46093.722222222219</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>107</v>
       </c>
@@ -4709,8 +6438,17 @@
       <c r="C131" s="5">
         <v>46092.826388888891</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F131" s="4">
+        <v>125</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H131" s="10">
+        <v>46093.72152777778</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>108</v>
       </c>
@@ -4720,8 +6458,17 @@
       <c r="C132" s="5">
         <v>46092.822916666664</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F132" s="4">
+        <v>126</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H132" s="10">
+        <v>46093.720833333333</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>109</v>
       </c>
@@ -4731,8 +6478,17 @@
       <c r="C133" s="5">
         <v>46092.822222222225</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F133" s="4">
+        <v>127</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H133" s="10">
+        <v>46093.720138888886</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>110</v>
       </c>
@@ -4742,8 +6498,17 @@
       <c r="C134" s="5">
         <v>46092.822222222225</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F134" s="4">
+        <v>128</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="H134" s="10">
+        <v>46093.718055555553</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>111</v>
       </c>
@@ -4753,8 +6518,17 @@
       <c r="C135" s="5">
         <v>46092.820833333331</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F135" s="4">
+        <v>129</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H135" s="10">
+        <v>46093.71597222222</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>112</v>
       </c>
@@ -4764,8 +6538,17 @@
       <c r="C136" s="5">
         <v>46092.820833333331</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F136" s="4">
+        <v>130</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H136" s="10">
+        <v>46093.714583333334</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>113</v>
       </c>
@@ -4775,8 +6558,17 @@
       <c r="C137" s="5">
         <v>46092.820138888892</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F137" s="4">
+        <v>131</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H137" s="10">
+        <v>46093.713888888888</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>114</v>
       </c>
@@ -4786,8 +6578,17 @@
       <c r="C138" s="5">
         <v>46092.819444444445</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F138" s="4">
+        <v>132</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H138" s="10">
+        <v>46093.712500000001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>115</v>
       </c>
@@ -4797,8 +6598,17 @@
       <c r="C139" s="5">
         <v>46092.818749999999</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F139" s="3">
+        <v>133</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H139" s="10">
+        <v>46093.712500000001</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>116</v>
       </c>
@@ -4808,8 +6618,17 @@
       <c r="C140" s="5">
         <v>46092.818055555559</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F140" s="4">
+        <v>134</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H140" s="10">
+        <v>46093.711111111108</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>117</v>
       </c>
@@ -4819,8 +6638,17 @@
       <c r="C141" s="5">
         <v>46092.817361111112</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F141" s="4">
+        <v>135</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H141" s="10">
+        <v>46093.709722222222</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>118</v>
       </c>
@@ -4830,8 +6658,17 @@
       <c r="C142" s="5">
         <v>46092.817361111112</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F142" s="4">
+        <v>136</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H142" s="10">
+        <v>46093.706944444442</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>119</v>
       </c>
@@ -4841,8 +6678,17 @@
       <c r="C143" s="5">
         <v>46092.816666666666</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F143" s="4">
+        <v>137</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H143" s="10">
+        <v>46093.706250000003</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>120</v>
       </c>
@@ -4852,8 +6698,17 @@
       <c r="C144" s="5">
         <v>46092.813888888886</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F144" s="4">
+        <v>138</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H144" s="10">
+        <v>46093.706250000003</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>121</v>
       </c>
@@ -4863,8 +6718,17 @@
       <c r="C145" s="5">
         <v>46092.8125</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F145" s="4">
+        <v>139</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H145" s="10">
+        <v>46093.706250000003</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>122</v>
       </c>
@@ -4874,8 +6738,17 @@
       <c r="C146" s="5">
         <v>46092.8125</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F146" s="4">
+        <v>140</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H146" s="10">
+        <v>46093.705555555556</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>123</v>
       </c>
@@ -4885,8 +6758,17 @@
       <c r="C147" s="5">
         <v>46092.80972222222</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F147" s="4">
+        <v>141</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H147" s="10">
+        <v>46093.705555555556</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>124</v>
       </c>
@@ -4896,8 +6778,17 @@
       <c r="C148" s="5">
         <v>46092.80972222222</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F148" s="4">
+        <v>142</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="H148" s="10">
+        <v>46093.705555555556</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>125</v>
       </c>
@@ -4907,8 +6798,17 @@
       <c r="C149" s="5">
         <v>46092.809027777781</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F149" s="4">
+        <v>143</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="H149" s="10">
+        <v>46093.704861111109</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>126</v>
       </c>
@@ -4918,8 +6818,17 @@
       <c r="C150" s="5">
         <v>46092.808333333334</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F150" s="4">
+        <v>144</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H150" s="10">
+        <v>46093.70208333333</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>127</v>
       </c>
@@ -4929,8 +6838,17 @@
       <c r="C151" s="5">
         <v>46092.806944444441</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F151" s="3">
+        <v>145</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H151" s="10">
+        <v>46093.70208333333</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>128</v>
       </c>
@@ -4940,8 +6858,17 @@
       <c r="C152" s="5">
         <v>46092.806944444441</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F152" s="4">
+        <v>146</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H152" s="10">
+        <v>46093.701388888891</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>129</v>
       </c>
@@ -4951,8 +6878,17 @@
       <c r="C153" s="5">
         <v>46092.806944444441</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F153" s="4">
+        <v>147</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H153" s="10">
+        <v>46093.701388888891</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>130</v>
       </c>
@@ -4962,8 +6898,17 @@
       <c r="C154" s="5">
         <v>46092.806250000001</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F154" s="4">
+        <v>148</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H154" s="10">
+        <v>46093.699305555558</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>131</v>
       </c>
@@ -4973,8 +6918,17 @@
       <c r="C155" s="5">
         <v>46092.806250000001</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F155" s="4">
+        <v>149</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H155" s="10">
+        <v>46093.698611111111</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>132</v>
       </c>
@@ -4984,8 +6938,17 @@
       <c r="C156" s="5">
         <v>46092.805555555555</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F156" s="4">
+        <v>150</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H156" s="10">
+        <v>46093.697916666664</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>133</v>
       </c>
@@ -4995,8 +6958,17 @@
       <c r="C157" s="5">
         <v>46092.804861111108</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F157" s="4">
+        <v>151</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H157" s="10">
+        <v>46093.697222222225</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>134</v>
       </c>
@@ -5006,8 +6978,17 @@
       <c r="C158" s="5">
         <v>46092.804861111108</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F158" s="4">
+        <v>152</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H158" s="10">
+        <v>46093.695833333331</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>135</v>
       </c>
@@ -5017,8 +6998,17 @@
       <c r="C159" s="5">
         <v>46092.804861111108</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F159" s="4">
+        <v>153</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H159" s="10">
+        <v>46093.695833333331</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>136</v>
       </c>
@@ -5028,8 +7018,17 @@
       <c r="C160" s="5">
         <v>46092.804166666669</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F160" s="4">
+        <v>154</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H160" s="10">
+        <v>46093.693749999999</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>137</v>
       </c>
@@ -5039,8 +7038,17 @@
       <c r="C161" s="5">
         <v>46092.804166666669</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F161" s="4">
+        <v>155</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H161" s="10">
+        <v>46093.693749999999</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>138</v>
       </c>
@@ -5050,8 +7058,17 @@
       <c r="C162" s="5">
         <v>46092.802777777775</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F162" s="4">
+        <v>156</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H162" s="10">
+        <v>46093.691666666666</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>139</v>
       </c>
@@ -5061,8 +7078,17 @@
       <c r="C163" s="5">
         <v>46092.802777777775</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F163" s="3">
+        <v>157</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H163" s="10">
+        <v>46093.691666666666</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>140</v>
       </c>
@@ -5072,8 +7098,17 @@
       <c r="C164" s="5">
         <v>46092.802083333336</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F164" s="4">
+        <v>158</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H164" s="10">
+        <v>46093.69027777778</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>141</v>
       </c>
@@ -5083,8 +7118,17 @@
       <c r="C165" s="5">
         <v>46092.802083333336</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F165" s="4">
+        <v>159</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H165" s="10">
+        <v>46093.69027777778</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>142</v>
       </c>
@@ -5094,8 +7138,17 @@
       <c r="C166" s="5">
         <v>46092.800694444442</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F166" s="4">
+        <v>160</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H166" s="10">
+        <v>46093.689583333333</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>143</v>
       </c>
@@ -5105,8 +7158,17 @@
       <c r="C167" s="5">
         <v>46092.800000000003</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F167" s="4">
+        <v>161</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H167" s="10">
+        <v>46093.688194444447</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>144</v>
       </c>
@@ -5116,8 +7178,17 @@
       <c r="C168" s="5">
         <v>46092.800000000003</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F168" s="4">
+        <v>162</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H168" s="10">
+        <v>46093.6875</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>145</v>
       </c>
@@ -5127,8 +7198,17 @@
       <c r="C169" s="5">
         <v>46092.800000000003</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F169" s="4">
+        <v>163</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H169" s="10">
+        <v>46093.686111111114</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>146</v>
       </c>
@@ -5138,8 +7218,17 @@
       <c r="C170" s="5">
         <v>46092.798611111109</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F170" s="4">
+        <v>164</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H170" s="10">
+        <v>46093.683333333334</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>147</v>
       </c>
@@ -5149,8 +7238,17 @@
       <c r="C171" s="5">
         <v>46092.79791666667</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F171" s="4">
+        <v>165</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H171" s="10">
+        <v>46093.682638888888</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>148</v>
       </c>
@@ -5160,8 +7258,17 @@
       <c r="C172" s="5">
         <v>46092.79791666667</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F172" s="4">
+        <v>166</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H172" s="10">
+        <v>46093.679861111108</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>149</v>
       </c>
@@ -5171,8 +7278,17 @@
       <c r="C173" s="5">
         <v>46092.79791666667</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F173" s="4">
+        <v>167</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H173" s="10">
+        <v>46093.679861111108</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>150</v>
       </c>
@@ -5182,8 +7298,17 @@
       <c r="C174" s="5">
         <v>46092.797222222223</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F174" s="4">
+        <v>168</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H174" s="10">
+        <v>46093.673611111109</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>151</v>
       </c>
@@ -5193,8 +7318,17 @@
       <c r="C175" s="5">
         <v>46092.797222222223</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F175" s="3">
+        <v>169</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H175" s="10">
+        <v>46093.670138888891</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>152</v>
       </c>
@@ -5204,8 +7338,17 @@
       <c r="C176" s="5">
         <v>46092.796527777777</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F176" s="4">
+        <v>170</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H176" s="10">
+        <v>46093.669444444444</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>153</v>
       </c>
@@ -5215,8 +7358,17 @@
       <c r="C177" s="5">
         <v>46092.796527777777</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F177" s="4">
+        <v>171</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H177" s="10">
+        <v>46093.668749999997</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>154</v>
       </c>
@@ -5226,8 +7378,17 @@
       <c r="C178" s="5">
         <v>46092.79583333333</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F178" s="4">
+        <v>172</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H178" s="10">
+        <v>46093.668055555558</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>155</v>
       </c>
@@ -5237,8 +7398,17 @@
       <c r="C179" s="5">
         <v>46092.79583333333</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F179" s="4">
+        <v>173</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H179" s="10">
+        <v>46093.667361111111</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>156</v>
       </c>
@@ -5248,8 +7418,17 @@
       <c r="C180" s="5">
         <v>46092.794444444444</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F180" s="4">
+        <v>174</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H180" s="10">
+        <v>46093.667361111111</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>157</v>
       </c>
@@ -5259,8 +7438,17 @@
       <c r="C181" s="5">
         <v>46092.793749999997</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F181" s="4">
+        <v>175</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H181" s="10">
+        <v>46093.666666666664</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
         <v>158</v>
       </c>
@@ -5270,8 +7458,17 @@
       <c r="C182" s="5">
         <v>46092.793749999997</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F182" s="4">
+        <v>176</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H182" s="10">
+        <v>46093.665277777778</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>159</v>
       </c>
@@ -5281,8 +7478,17 @@
       <c r="C183" s="5">
         <v>46092.793749999997</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F183" s="4">
+        <v>177</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H183" s="10">
+        <v>46093.665277777778</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>160</v>
       </c>
@@ -5292,8 +7498,17 @@
       <c r="C184" s="5">
         <v>46092.792361111111</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F184" s="4">
+        <v>178</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H184" s="10">
+        <v>46093.665277777778</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>161</v>
       </c>
@@ -5303,8 +7518,17 @@
       <c r="C185" s="5">
         <v>46092.792361111111</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F185" s="4">
+        <v>179</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H185" s="10">
+        <v>46093.664583333331</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>162</v>
       </c>
@@ -5314,8 +7538,17 @@
       <c r="C186" s="5">
         <v>46092.791666666664</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F186" s="4">
+        <v>180</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H186" s="10">
+        <v>46093.664583333331</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>163</v>
       </c>
@@ -5325,8 +7558,17 @@
       <c r="C187" s="5">
         <v>46092.790277777778</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F187" s="3">
+        <v>181</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H187" s="10">
+        <v>46093.663888888892</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>164</v>
       </c>
@@ -5336,8 +7578,17 @@
       <c r="C188" s="5">
         <v>46092.788194444445</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F188" s="4">
+        <v>182</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="H188" s="10">
+        <v>46093.661805555559</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>165</v>
       </c>
@@ -5347,8 +7598,17 @@
       <c r="C189" s="5">
         <v>46092.788194444445</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F189" s="4">
+        <v>183</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H189" s="10">
+        <v>46093.661111111112</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>166</v>
       </c>
@@ -5358,8 +7618,17 @@
       <c r="C190" s="5">
         <v>46092.787499999999</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F190" s="4">
+        <v>184</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H190" s="10">
+        <v>46093.659722222219</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>167</v>
       </c>
@@ -5369,8 +7638,17 @@
       <c r="C191" s="5">
         <v>46092.785416666666</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F191" s="4">
+        <v>185</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H191" s="10">
+        <v>46093.657638888886</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>168</v>
       </c>
@@ -5380,8 +7658,17 @@
       <c r="C192" s="5">
         <v>46092.785416666666</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F192" s="4">
+        <v>186</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H192" s="10">
+        <v>46093.656944444447</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>169</v>
       </c>
@@ -5391,8 +7678,17 @@
       <c r="C193" s="5">
         <v>46092.784722222219</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F193" s="4">
+        <v>187</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H193" s="10">
+        <v>46093.655555555553</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>170</v>
       </c>
@@ -5402,8 +7698,17 @@
       <c r="C194" s="5">
         <v>46092.784722222219</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F194" s="4">
+        <v>188</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H194" s="10">
+        <v>46093.654861111114</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>171</v>
       </c>
@@ -5413,8 +7718,17 @@
       <c r="C195" s="5">
         <v>46092.784722222219</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F195" s="4">
+        <v>189</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H195" s="10">
+        <v>46093.654861111114</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>172</v>
       </c>
@@ -5424,8 +7738,17 @@
       <c r="C196" s="5">
         <v>46092.78402777778</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F196" s="4">
+        <v>190</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="H196" s="10">
+        <v>46093.654166666667</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>173</v>
       </c>
@@ -5435,8 +7758,17 @@
       <c r="C197" s="5">
         <v>46092.78402777778</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F197" s="4">
+        <v>191</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H197" s="10">
+        <v>46093.652777777781</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>174</v>
       </c>
@@ -5446,8 +7778,17 @@
       <c r="C198" s="5">
         <v>46092.783333333333</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F198" s="4">
+        <v>192</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H198" s="10">
+        <v>46093.652777777781</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>175</v>
       </c>
@@ -5457,8 +7798,17 @@
       <c r="C199" s="5">
         <v>46092.783333333333</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F199" s="3">
+        <v>193</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H199" s="10">
+        <v>46093.652083333334</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>176</v>
       </c>
@@ -5468,8 +7818,17 @@
       <c r="C200" s="5">
         <v>46092.783333333333</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F200" s="4">
+        <v>194</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H200" s="10">
+        <v>46093.651388888888</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>177</v>
       </c>
@@ -5479,8 +7838,17 @@
       <c r="C201" s="5">
         <v>46092.782638888886</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F201" s="4">
+        <v>195</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H201" s="10">
+        <v>46093.650694444441</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>178</v>
       </c>
@@ -5490,8 +7858,17 @@
       <c r="C202" s="5">
         <v>46092.782638888886</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F202" s="4">
+        <v>196</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H202" s="10">
+        <v>46093.65</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>179</v>
       </c>
@@ -5501,8 +7878,17 @@
       <c r="C203" s="5">
         <v>46092.781944444447</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F203" s="4">
+        <v>197</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H203" s="10">
+        <v>46093.65</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
         <v>180</v>
       </c>
@@ -5512,8 +7898,17 @@
       <c r="C204" s="5">
         <v>46092.781944444447</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F204" s="4">
+        <v>198</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="H204" s="10">
+        <v>46093.649305555555</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>181</v>
       </c>
@@ -5523,8 +7918,17 @@
       <c r="C205" s="5">
         <v>46092.781944444447</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F205" s="4">
+        <v>199</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H205" s="10">
+        <v>46093.649305555555</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>182</v>
       </c>
@@ -5534,8 +7938,17 @@
       <c r="C206" s="5">
         <v>46092.781944444447</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F206" s="4">
+        <v>200</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H206" s="10">
+        <v>46093.647916666669</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>183</v>
       </c>
@@ -5545,8 +7958,17 @@
       <c r="C207" s="5">
         <v>46092.78125</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F207" s="4">
+        <v>201</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H207" s="10">
+        <v>46093.647222222222</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>184</v>
       </c>
@@ -5555,6 +7977,15 @@
       </c>
       <c r="C208" s="5">
         <v>46092.780555555553</v>
+      </c>
+      <c r="F208" s="4">
+        <v>202</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H208" s="10">
+        <v>46093.647222222222</v>
       </c>
     </row>
     <row r="209" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">

--- a/numbers.xlsx
+++ b/numbers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nodir\Projects\open-budget-search\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9C5CC6-A1EC-453D-B0F0-4B57D4E3DD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705965E2-B3FE-4DCE-9A07-A68D3CB84289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0AABE945-EFF0-4E0B-A9BD-4BB876D9C82D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="1395">
   <si>
     <t>**-*14-63-61</t>
   </si>
@@ -3493,6 +3493,732 @@
   </si>
   <si>
     <t>**-*94-01-81</t>
+  </si>
+  <si>
+    <t>**-*99-62-12</t>
+  </si>
+  <si>
+    <t>**-*18-92-90</t>
+  </si>
+  <si>
+    <t>**-*64-46-87</t>
+  </si>
+  <si>
+    <t>**-*43-72-51</t>
+  </si>
+  <si>
+    <t>**-*70-07-96</t>
+  </si>
+  <si>
+    <t>**-*70-01-99</t>
+  </si>
+  <si>
+    <t>**-*00-21-13</t>
+  </si>
+  <si>
+    <t>**-*38-23-95</t>
+  </si>
+  <si>
+    <t>**-*90-84-91</t>
+  </si>
+  <si>
+    <t>**-*75-70-28</t>
+  </si>
+  <si>
+    <t>**-*70-67-67</t>
+  </si>
+  <si>
+    <t>**-*23-93-90</t>
+  </si>
+  <si>
+    <t>**-*40-88-95</t>
+  </si>
+  <si>
+    <t>**-*17-59-07</t>
+  </si>
+  <si>
+    <t>**-*61-10-98</t>
+  </si>
+  <si>
+    <t>**-*41-26-02</t>
+  </si>
+  <si>
+    <t>**-*75-52-05</t>
+  </si>
+  <si>
+    <t>**-*14-96-01</t>
+  </si>
+  <si>
+    <t>**-*73-74-88</t>
+  </si>
+  <si>
+    <t>**-*12-21-95</t>
+  </si>
+  <si>
+    <t>**-*16-80-87</t>
+  </si>
+  <si>
+    <t>**-*86-87-47</t>
+  </si>
+  <si>
+    <t>**-*11-62-44</t>
+  </si>
+  <si>
+    <t>**-*48-82-81</t>
+  </si>
+  <si>
+    <t>**-*50-38-86</t>
+  </si>
+  <si>
+    <t>**-*34-08-01</t>
+  </si>
+  <si>
+    <t>**-*05-63-99</t>
+  </si>
+  <si>
+    <t>**-*73-74-92</t>
+  </si>
+  <si>
+    <t>**-*53-77-43</t>
+  </si>
+  <si>
+    <t>**-*70-02-52</t>
+  </si>
+  <si>
+    <t>**-*55-88-95</t>
+  </si>
+  <si>
+    <t>**-*66-05-12</t>
+  </si>
+  <si>
+    <t>**-*10-90-96</t>
+  </si>
+  <si>
+    <t>**-*00-44-23</t>
+  </si>
+  <si>
+    <t>**-*23-87-78</t>
+  </si>
+  <si>
+    <t>**-*10-91-68</t>
+  </si>
+  <si>
+    <t>**-*82-86-89</t>
+  </si>
+  <si>
+    <t>**-*16-30-33</t>
+  </si>
+  <si>
+    <t>**-*29-23-57</t>
+  </si>
+  <si>
+    <t>**-*84-85-87</t>
+  </si>
+  <si>
+    <t>**-*76-30-02</t>
+  </si>
+  <si>
+    <t>**-*65-30-95</t>
+  </si>
+  <si>
+    <t>**-*83-12-57</t>
+  </si>
+  <si>
+    <t>**-*16-95-98</t>
+  </si>
+  <si>
+    <t>**-*13-73-14</t>
+  </si>
+  <si>
+    <t>**-*94-55-60</t>
+  </si>
+  <si>
+    <t>**-*53-32-02</t>
+  </si>
+  <si>
+    <t>**-*78-77-36</t>
+  </si>
+  <si>
+    <t>**-*71-89-88</t>
+  </si>
+  <si>
+    <t>**-*16-34-71</t>
+  </si>
+  <si>
+    <t>**-*82-39-85</t>
+  </si>
+  <si>
+    <t>**-*86-20-77</t>
+  </si>
+  <si>
+    <t>**-*86-25-80</t>
+  </si>
+  <si>
+    <t>**-*19-82-86</t>
+  </si>
+  <si>
+    <t>**-*91-00-65</t>
+  </si>
+  <si>
+    <t>**-*61-19-89</t>
+  </si>
+  <si>
+    <t>**-*11-94-11</t>
+  </si>
+  <si>
+    <t>**-*10-15-16</t>
+  </si>
+  <si>
+    <t>**-*29-22-82</t>
+  </si>
+  <si>
+    <t>**-*83-77-27</t>
+  </si>
+  <si>
+    <t>**-*20-66-53</t>
+  </si>
+  <si>
+    <t>**-*69-91-50</t>
+  </si>
+  <si>
+    <t>**-*43-39-36</t>
+  </si>
+  <si>
+    <t>**-*23-83-05</t>
+  </si>
+  <si>
+    <t>**-*83-09-81</t>
+  </si>
+  <si>
+    <t>**-*82-63-77</t>
+  </si>
+  <si>
+    <t>**-*60-10-79</t>
+  </si>
+  <si>
+    <t>**-*36-85-86</t>
+  </si>
+  <si>
+    <t>**-*38-60-08</t>
+  </si>
+  <si>
+    <t>**-*60-42-42</t>
+  </si>
+  <si>
+    <t>**-*34-00-87</t>
+  </si>
+  <si>
+    <t>**-*60-06-07</t>
+  </si>
+  <si>
+    <t>**-*10-73-85</t>
+  </si>
+  <si>
+    <t>**-*88-68-78</t>
+  </si>
+  <si>
+    <t>**-*71-38-81</t>
+  </si>
+  <si>
+    <t>**-*17-91-87</t>
+  </si>
+  <si>
+    <t>**-*36-25-85</t>
+  </si>
+  <si>
+    <t>**-*11-40-07</t>
+  </si>
+  <si>
+    <t>**-*04-16-61</t>
+  </si>
+  <si>
+    <t>**-*50-91-93</t>
+  </si>
+  <si>
+    <t>**-*82-20-29</t>
+  </si>
+  <si>
+    <t>**-*90-14-82</t>
+  </si>
+  <si>
+    <t>**-*03-28-69</t>
+  </si>
+  <si>
+    <t>**-*19-29-89</t>
+  </si>
+  <si>
+    <t>**-*09-01-80</t>
+  </si>
+  <si>
+    <t>**-*97-51-28</t>
+  </si>
+  <si>
+    <t>**-*13-42-33</t>
+  </si>
+  <si>
+    <t>**-*47-90-02</t>
+  </si>
+  <si>
+    <t>**-*57-48-08</t>
+  </si>
+  <si>
+    <t>**-*22-20-64</t>
+  </si>
+  <si>
+    <t>**-*22-27-26</t>
+  </si>
+  <si>
+    <t>**-*99-95-19</t>
+  </si>
+  <si>
+    <t>**-*25-86-65</t>
+  </si>
+  <si>
+    <t>**-*85-21-98</t>
+  </si>
+  <si>
+    <t>**-*19-16-84</t>
+  </si>
+  <si>
+    <t>**-*22-91-97</t>
+  </si>
+  <si>
+    <t>**-*05-16-58</t>
+  </si>
+  <si>
+    <t>**-*14-20-92</t>
+  </si>
+  <si>
+    <t>**-*99-04-24</t>
+  </si>
+  <si>
+    <t>**-*39-21-30</t>
+  </si>
+  <si>
+    <t>**-*23-91-41</t>
+  </si>
+  <si>
+    <t>**-*15-25-79</t>
+  </si>
+  <si>
+    <t>**-*29-77-06</t>
+  </si>
+  <si>
+    <t>**-*75-20-91</t>
+  </si>
+  <si>
+    <t>**-*46-61-00</t>
+  </si>
+  <si>
+    <t>**-*75-11-01</t>
+  </si>
+  <si>
+    <t>**-*43-01-54</t>
+  </si>
+  <si>
+    <t>**-*88-18-00</t>
+  </si>
+  <si>
+    <t>**-*74-74-70</t>
+  </si>
+  <si>
+    <t>**-*17-17-92</t>
+  </si>
+  <si>
+    <t>**-*38-28-03</t>
+  </si>
+  <si>
+    <t>**-*70-29-53</t>
+  </si>
+  <si>
+    <t>**-*00-12-70</t>
+  </si>
+  <si>
+    <t>**-*77-27-24</t>
+  </si>
+  <si>
+    <t>**-*00-03-81</t>
+  </si>
+  <si>
+    <t>**-*20-75-90</t>
+  </si>
+  <si>
+    <t>**-*92-07-10</t>
+  </si>
+  <si>
+    <t>**-*13-57-25</t>
+  </si>
+  <si>
+    <t>**-*37-74-34</t>
+  </si>
+  <si>
+    <t>**-*44-18-75</t>
+  </si>
+  <si>
+    <t>**-*70-00-09</t>
+  </si>
+  <si>
+    <t>**-*12-30-40</t>
+  </si>
+  <si>
+    <t>**-*81-71-90</t>
+  </si>
+  <si>
+    <t>**-*58-33-66</t>
+  </si>
+  <si>
+    <t>**-*47-28-84</t>
+  </si>
+  <si>
+    <t>**-*11-75-80</t>
+  </si>
+  <si>
+    <t>**-*11-12-06</t>
+  </si>
+  <si>
+    <t>**-*19-65-25</t>
+  </si>
+  <si>
+    <t>**-*79-83-79</t>
+  </si>
+  <si>
+    <t>**-*45-97-04</t>
+  </si>
+  <si>
+    <t>**-*11-84-11</t>
+  </si>
+  <si>
+    <t>**-*83-53-20</t>
+  </si>
+  <si>
+    <t>**-*82-62-97</t>
+  </si>
+  <si>
+    <t>**-*90-50-74</t>
+  </si>
+  <si>
+    <t>**-*97-68-10</t>
+  </si>
+  <si>
+    <t>**-*83-46-63</t>
+  </si>
+  <si>
+    <t>**-*19-73-97</t>
+  </si>
+  <si>
+    <t>**-*75-91-94</t>
+  </si>
+  <si>
+    <t>**-*92-37-20</t>
+  </si>
+  <si>
+    <t>**-*26-76-77</t>
+  </si>
+  <si>
+    <t>**-*58-08-05</t>
+  </si>
+  <si>
+    <t>**-*18-66-80</t>
+  </si>
+  <si>
+    <t>**-*77-71-72</t>
+  </si>
+  <si>
+    <t>**-*76-66-20</t>
+  </si>
+  <si>
+    <t>**-*37-24-07</t>
+  </si>
+  <si>
+    <t>**-*53-01-15</t>
+  </si>
+  <si>
+    <t>**-*15-20-71</t>
+  </si>
+  <si>
+    <t>**-*82-85-94</t>
+  </si>
+  <si>
+    <t>**-*10-04-78</t>
+  </si>
+  <si>
+    <t>**-*20-97-01</t>
+  </si>
+  <si>
+    <t>**-*51-28-24</t>
+  </si>
+  <si>
+    <t>**-*25-92-02</t>
+  </si>
+  <si>
+    <t>**-*51-03-93</t>
+  </si>
+  <si>
+    <t>**-*17-11-14</t>
+  </si>
+  <si>
+    <t>**-*51-44-43</t>
+  </si>
+  <si>
+    <t>**-*98-84-21</t>
+  </si>
+  <si>
+    <t>**-*04-65-04</t>
+  </si>
+  <si>
+    <t>**-*84-09-01</t>
+  </si>
+  <si>
+    <t>**-*57-20-08</t>
+  </si>
+  <si>
+    <t>**-*16-14-94</t>
+  </si>
+  <si>
+    <t>**-*00-67-87</t>
+  </si>
+  <si>
+    <t>**-*53-21-29</t>
+  </si>
+  <si>
+    <t>**-*19-27-72</t>
+  </si>
+  <si>
+    <t>**-*12-40-10</t>
+  </si>
+  <si>
+    <t>**-*54-38-28</t>
+  </si>
+  <si>
+    <t>**-*48-40-05</t>
+  </si>
+  <si>
+    <t>**-*90-69-72</t>
+  </si>
+  <si>
+    <t>**-*17-22-69</t>
+  </si>
+  <si>
+    <t>**-*72-14-30</t>
+  </si>
+  <si>
+    <t>**-*49-52-32</t>
+  </si>
+  <si>
+    <t>**-*29-06-99</t>
+  </si>
+  <si>
+    <t>**-*15-20-19</t>
+  </si>
+  <si>
+    <t>**-*70-04-90</t>
+  </si>
+  <si>
+    <t>**-*62-08-28</t>
+  </si>
+  <si>
+    <t>**-*05-55-35</t>
+  </si>
+  <si>
+    <t>**-*49-06-91</t>
+  </si>
+  <si>
+    <t>**-*80-90-85</t>
+  </si>
+  <si>
+    <t>**-*82-05-04</t>
+  </si>
+  <si>
+    <t>**-*56-30-38</t>
+  </si>
+  <si>
+    <t>**-*72-79-74</t>
+  </si>
+  <si>
+    <t>**-*44-94-32</t>
+  </si>
+  <si>
+    <t>**-*57-58-07</t>
+  </si>
+  <si>
+    <t>**-*29-18-65</t>
+  </si>
+  <si>
+    <t>**-*82-23-71</t>
+  </si>
+  <si>
+    <t>**-*74-01-74</t>
+  </si>
+  <si>
+    <t>**-*93-25-93</t>
+  </si>
+  <si>
+    <t>**-*17-19-79</t>
+  </si>
+  <si>
+    <t>**-*22-57-87</t>
+  </si>
+  <si>
+    <t>**-*09-08-04</t>
+  </si>
+  <si>
+    <t>**-*37-37-66</t>
+  </si>
+  <si>
+    <t>**-*86-57-27</t>
+  </si>
+  <si>
+    <t>**-*15-02-53</t>
+  </si>
+  <si>
+    <t>**-*21-01-62</t>
+  </si>
+  <si>
+    <t>**-*20-86-84</t>
+  </si>
+  <si>
+    <t>**-*31-50-49</t>
+  </si>
+  <si>
+    <t>**-*51-27-29</t>
+  </si>
+  <si>
+    <t>**-*84-50-28</t>
+  </si>
+  <si>
+    <t>**-*11-64-34</t>
+  </si>
+  <si>
+    <t>**-*10-76-01</t>
+  </si>
+  <si>
+    <t>**-*87-30-04</t>
+  </si>
+  <si>
+    <t>**-*49-08-85</t>
+  </si>
+  <si>
+    <t>**-*43-95-33</t>
+  </si>
+  <si>
+    <t>**-*71-61-86</t>
+  </si>
+  <si>
+    <t>**-*58-19-87</t>
+  </si>
+  <si>
+    <t>**-*29-40-86</t>
+  </si>
+  <si>
+    <t>**-*43-69-85</t>
+  </si>
+  <si>
+    <t>**-*25-19-99</t>
+  </si>
+  <si>
+    <t>**-*42-20-10</t>
+  </si>
+  <si>
+    <t>**-*22-55-97</t>
+  </si>
+  <si>
+    <t>**-*92-35-99</t>
+  </si>
+  <si>
+    <t>**-*02-09-88</t>
+  </si>
+  <si>
+    <t>**-*80-23-27</t>
+  </si>
+  <si>
+    <t>**-*23-40-94</t>
+  </si>
+  <si>
+    <t>**-*98-98-26</t>
+  </si>
+  <si>
+    <t>**-*22-09-23</t>
+  </si>
+  <si>
+    <t>**-*85-28-28</t>
+  </si>
+  <si>
+    <t>**-*37-90-62</t>
+  </si>
+  <si>
+    <t>**-*93-58-00</t>
+  </si>
+  <si>
+    <t>**-*12-82-05</t>
+  </si>
+  <si>
+    <t>**-*74-21-90</t>
+  </si>
+  <si>
+    <t>**-*70-31-36</t>
+  </si>
+  <si>
+    <t>**-*76-79-39</t>
+  </si>
+  <si>
+    <t>**-*20-53-58</t>
+  </si>
+  <si>
+    <t>**-*02-14-11</t>
+  </si>
+  <si>
+    <t>**-*57-00-22</t>
+  </si>
+  <si>
+    <t>**-*05-76-76</t>
+  </si>
+  <si>
+    <t>**-*57-37-95</t>
+  </si>
+  <si>
+    <t>**-*66-24-94</t>
+  </si>
+  <si>
+    <t>**-*72-02-06</t>
+  </si>
+  <si>
+    <t>**-*12-83-87</t>
+  </si>
+  <si>
+    <t>**-*21-04-94</t>
+  </si>
+  <si>
+    <t>**-*91-07-08</t>
+  </si>
+  <si>
+    <t>**-*36-99-94</t>
+  </si>
+  <si>
+    <t>**-*71-19-82</t>
+  </si>
+  <si>
+    <t>**-*28-65-21</t>
+  </si>
+  <si>
+    <t>**-*13-90-86</t>
+  </si>
+  <si>
+    <t>**-*42-29-63</t>
+  </si>
+  <si>
+    <t>**-*36-85-51</t>
+  </si>
+  <si>
+    <t>**-*26-21-09</t>
+  </si>
+  <si>
+    <t>**-*61-00-95</t>
+  </si>
+  <si>
+    <t>**-*28-58-61</t>
+  </si>
+  <si>
+    <t>**-*70-66-69</t>
   </si>
 </sst>
 </file>
@@ -3501,7 +4227,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy\ hh:mm:ss"/>
-    <numFmt numFmtId="171" formatCode="dd\-mm\-yyyy\ hh:mm"/>
+    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy\ hh:mm"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -3620,7 +4346,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3938,7 +4664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA66EC08-8D26-46AA-A6AA-1D6A0B4C73D5}">
-  <dimension ref="A7:H973"/>
+  <dimension ref="A7:M973"/>
   <sheetFormatPr defaultRowHeight="21" thickBottom="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25.28515625" customWidth="1"/>
@@ -3946,9 +4672,11 @@
     <col min="6" max="6" width="6.5703125" customWidth="1"/>
     <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="29.28515625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="20.5703125" customWidth="1"/>
+    <col min="13" max="13" width="27" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3967,8 +4695,17 @@
       <c r="H7" s="10">
         <v>46094.332638888889</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="3">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="M7" s="10">
+        <v>46094.785416666666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>2</v>
       </c>
@@ -3987,8 +4724,17 @@
       <c r="H8" s="10">
         <v>46094.331944444442</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="4">
+        <v>2</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M8" s="10">
+        <v>46094.772916666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>3</v>
       </c>
@@ -4007,8 +4753,17 @@
       <c r="H9" s="10">
         <v>46094.331944444442</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="4">
+        <v>3</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="M9" s="10">
+        <v>46094.771527777775</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>4</v>
       </c>
@@ -4027,8 +4782,17 @@
       <c r="H10" s="10">
         <v>46094.322222222225</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="4">
+        <v>4</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="M10" s="10">
+        <v>46094.763194444444</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>5</v>
       </c>
@@ -4047,8 +4811,17 @@
       <c r="H11" s="10">
         <v>46094.321527777778</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="4">
+        <v>5</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="M11" s="10">
+        <v>46094.762499999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>6</v>
       </c>
@@ -4067,8 +4840,17 @@
       <c r="H12" s="10">
         <v>46094.320833333331</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="4">
+        <v>6</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="M12" s="10">
+        <v>46094.762499999997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>7</v>
       </c>
@@ -4087,8 +4869,17 @@
       <c r="H13" s="10">
         <v>46094.320138888892</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="4">
+        <v>7</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="M13" s="10">
+        <v>46094.761805555558</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>8</v>
       </c>
@@ -4107,8 +4898,17 @@
       <c r="H14" s="10">
         <v>46094.308333333334</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="4">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="M14" s="10">
+        <v>46094.760416666664</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>9</v>
       </c>
@@ -4127,8 +4927,17 @@
       <c r="H15" s="10">
         <v>46094.306944444441</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K15" s="4">
+        <v>9</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M15" s="10">
+        <v>46094.755555555559</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>10</v>
       </c>
@@ -4147,8 +4956,17 @@
       <c r="H16" s="10">
         <v>46094.298611111109</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="4">
+        <v>10</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="M16" s="10">
+        <v>46094.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>11</v>
       </c>
@@ -4167,8 +4985,17 @@
       <c r="H17" s="10">
         <v>46094.290277777778</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K17" s="4">
+        <v>11</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M17" s="10">
+        <v>46094.745138888888</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>12</v>
       </c>
@@ -4187,8 +5014,17 @@
       <c r="H18" s="10">
         <v>46094.284722222219</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="4">
+        <v>12</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="M18" s="10">
+        <v>46094.743055555555</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>13</v>
       </c>
@@ -4207,8 +5043,17 @@
       <c r="H19" s="10">
         <v>46094.272916666669</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K19" s="3">
+        <v>13</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="M19" s="10">
+        <v>46094.742361111108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>14</v>
       </c>
@@ -4227,8 +5072,17 @@
       <c r="H20" s="10">
         <v>46094.267361111109</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="4">
+        <v>14</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="M20" s="10">
+        <v>46094.738888888889</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>15</v>
       </c>
@@ -4247,8 +5101,17 @@
       <c r="H21" s="10">
         <v>46094.265972222223</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="4">
+        <v>15</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M21" s="10">
+        <v>46094.738888888889</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>16</v>
       </c>
@@ -4267,8 +5130,17 @@
       <c r="H22" s="10">
         <v>46094.255555555559</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K22" s="4">
+        <v>16</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="M22" s="10">
+        <v>46094.738194444442</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>17</v>
       </c>
@@ -4287,8 +5159,17 @@
       <c r="H23" s="10">
         <v>46094.238888888889</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K23" s="4">
+        <v>17</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M23" s="10">
+        <v>46094.738194444442</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>18</v>
       </c>
@@ -4307,8 +5188,17 @@
       <c r="H24" s="10">
         <v>46094.231249999997</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K24" s="4">
+        <v>18</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="M24" s="10">
+        <v>46094.737500000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>1</v>
       </c>
@@ -4327,8 +5217,17 @@
       <c r="H25" s="10">
         <v>46094.224999999999</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="4">
+        <v>19</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="M25" s="10">
+        <v>46094.73541666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>2</v>
       </c>
@@ -4347,8 +5246,17 @@
       <c r="H26" s="10">
         <v>46094.220138888886</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K26" s="4">
+        <v>20</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="M26" s="10">
+        <v>46094.734722222223</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>3</v>
       </c>
@@ -4367,8 +5275,17 @@
       <c r="H27" s="10">
         <v>46094.216666666667</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K27" s="4">
+        <v>21</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M27" s="10">
+        <v>46094.734722222223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>4</v>
       </c>
@@ -4387,8 +5304,17 @@
       <c r="H28" s="10">
         <v>46094.198611111111</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K28" s="4">
+        <v>22</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="M28" s="10">
+        <v>46094.732638888891</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>5</v>
       </c>
@@ -4407,8 +5333,17 @@
       <c r="H29" s="10">
         <v>46094.197916666664</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="4">
+        <v>23</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="M29" s="10">
+        <v>46094.729166666664</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>6</v>
       </c>
@@ -4427,8 +5362,17 @@
       <c r="H30" s="10">
         <v>46094.1875</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K30" s="4">
+        <v>24</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="M30" s="10">
+        <v>46094.728472222225</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>7</v>
       </c>
@@ -4447,8 +5391,17 @@
       <c r="H31" s="10">
         <v>46094.168055555558</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="3">
+        <v>25</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="M31" s="10">
+        <v>46094.722222222219</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>8</v>
       </c>
@@ -4467,8 +5420,17 @@
       <c r="H32" s="10">
         <v>46094.163194444445</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="4">
+        <v>26</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="M32" s="10">
+        <v>46094.714583333334</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>9</v>
       </c>
@@ -4487,8 +5449,17 @@
       <c r="H33" s="10">
         <v>46094.150694444441</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K33" s="4">
+        <v>27</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M33" s="10">
+        <v>46094.714583333334</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>10</v>
       </c>
@@ -4507,8 +5478,17 @@
       <c r="H34" s="10">
         <v>46094.15</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K34" s="4">
+        <v>28</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="M34" s="10">
+        <v>46094.710416666669</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>11</v>
       </c>
@@ -4527,8 +5507,17 @@
       <c r="H35" s="10">
         <v>46094.15</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K35" s="4">
+        <v>29</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="M35" s="10">
+        <v>46094.710416666669</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>12</v>
       </c>
@@ -4547,8 +5536,17 @@
       <c r="H36" s="10">
         <v>46094.134027777778</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K36" s="4">
+        <v>30</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M36" s="10">
+        <v>46094.708333333336</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>13</v>
       </c>
@@ -4567,8 +5565,17 @@
       <c r="H37" s="10">
         <v>46094.132638888892</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K37" s="4">
+        <v>31</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="M37" s="10">
+        <v>46094.708333333336</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>14</v>
       </c>
@@ -4587,8 +5594,17 @@
       <c r="H38" s="10">
         <v>46094.109027777777</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K38" s="4">
+        <v>32</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M38" s="10">
+        <v>46094.701388888891</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>15</v>
       </c>
@@ -4607,8 +5623,17 @@
       <c r="H39" s="10">
         <v>46094.081944444442</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K39" s="4">
+        <v>33</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="M39" s="10">
+        <v>46094.699305555558</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>16</v>
       </c>
@@ -4627,8 +5652,17 @@
       <c r="H40" s="10">
         <v>46094.081250000003</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K40" s="4">
+        <v>34</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="M40" s="10">
+        <v>46094.699305555558</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>17</v>
       </c>
@@ -4647,8 +5681,17 @@
       <c r="H41" s="10">
         <v>46094.071527777778</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K41" s="4">
+        <v>35</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="M41" s="10">
+        <v>46094.697916666664</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>18</v>
       </c>
@@ -4667,8 +5710,17 @@
       <c r="H42" s="10">
         <v>46094.038194444445</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K42" s="4">
+        <v>36</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="M42" s="10">
+        <v>46094.697222222225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>19</v>
       </c>
@@ -4687,8 +5739,17 @@
       <c r="H43" s="10">
         <v>46094.003472222219</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K43" s="3">
+        <v>37</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="M43" s="10">
+        <v>46094.695833333331</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>20</v>
       </c>
@@ -4707,8 +5768,17 @@
       <c r="H44" s="10">
         <v>46093.994444444441</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K44" s="4">
+        <v>38</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="M44" s="10">
+        <v>46094.694444444445</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>21</v>
       </c>
@@ -4727,8 +5797,17 @@
       <c r="H45" s="10">
         <v>46093.988194444442</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K45" s="4">
+        <v>39</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="M45" s="10">
+        <v>46094.693749999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>22</v>
       </c>
@@ -4747,8 +5826,17 @@
       <c r="H46" s="10">
         <v>46093.98541666667</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K46" s="4">
+        <v>40</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M46" s="10">
+        <v>46094.692361111112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>23</v>
       </c>
@@ -4767,8 +5855,17 @@
       <c r="H47" s="10">
         <v>46093.984027777777</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K47" s="4">
+        <v>41</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="M47" s="10">
+        <v>46094.690972222219</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>24</v>
       </c>
@@ -4787,8 +5884,17 @@
       <c r="H48" s="10">
         <v>46093.976388888892</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K48" s="4">
+        <v>42</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M48" s="10">
+        <v>46094.69027777778</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>25</v>
       </c>
@@ -4807,8 +5913,17 @@
       <c r="H49" s="10">
         <v>46093.973611111112</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K49" s="4">
+        <v>43</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="M49" s="10">
+        <v>46094.688888888886</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>26</v>
       </c>
@@ -4827,8 +5942,17 @@
       <c r="H50" s="10">
         <v>46093.972916666666</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K50" s="4">
+        <v>44</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="M50" s="10">
+        <v>46094.684027777781</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>27</v>
       </c>
@@ -4847,8 +5971,17 @@
       <c r="H51" s="10">
         <v>46093.961805555555</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K51" s="4">
+        <v>45</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M51" s="10">
+        <v>46094.67291666667</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>28</v>
       </c>
@@ -4867,8 +6000,17 @@
       <c r="H52" s="10">
         <v>46093.961111111108</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K52" s="4">
+        <v>46</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="M52" s="10">
+        <v>46094.67083333333</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>29</v>
       </c>
@@ -4887,8 +6029,17 @@
       <c r="H53" s="10">
         <v>46093.959722222222</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K53" s="4">
+        <v>47</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="M53" s="10">
+        <v>46094.669444444444</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>30</v>
       </c>
@@ -4907,8 +6058,17 @@
       <c r="H54" s="10">
         <v>46093.957638888889</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K54" s="4">
+        <v>48</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="M54" s="10">
+        <v>46094.669444444444</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>31</v>
       </c>
@@ -4927,8 +6087,17 @@
       <c r="H55" s="10">
         <v>46093.956250000003</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K55" s="3">
+        <v>49</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="M55" s="10">
+        <v>46094.669444444444</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>32</v>
       </c>
@@ -4947,8 +6116,17 @@
       <c r="H56" s="10">
         <v>46093.954861111109</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K56" s="4">
+        <v>50</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="M56" s="10">
+        <v>46094.663888888892</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>33</v>
       </c>
@@ -4967,8 +6145,17 @@
       <c r="H57" s="10">
         <v>46093.950694444444</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K57" s="4">
+        <v>51</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="M57" s="10">
+        <v>46094.661805555559</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>34</v>
       </c>
@@ -4987,8 +6174,17 @@
       <c r="H58" s="10">
         <v>46093.949305555558</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K58" s="4">
+        <v>52</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="M58" s="10">
+        <v>46094.659722222219</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>35</v>
       </c>
@@ -5007,8 +6203,17 @@
       <c r="H59" s="10">
         <v>46093.945833333331</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K59" s="4">
+        <v>53</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="M59" s="10">
+        <v>46094.658333333333</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>36</v>
       </c>
@@ -5027,8 +6232,17 @@
       <c r="H60" s="10">
         <v>46093.938888888886</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K60" s="4">
+        <v>54</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="M60" s="10">
+        <v>46094.656944444447</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>37</v>
       </c>
@@ -5047,8 +6261,17 @@
       <c r="H61" s="10">
         <v>46093.921527777777</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K61" s="4">
+        <v>55</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="M61" s="10">
+        <v>46094.654861111114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>38</v>
       </c>
@@ -5067,8 +6290,17 @@
       <c r="H62" s="10">
         <v>46093.92083333333</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K62" s="4">
+        <v>56</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M62" s="10">
+        <v>46094.654861111114</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>39</v>
       </c>
@@ -5087,8 +6319,17 @@
       <c r="H63" s="10">
         <v>46093.920138888891</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K63" s="4">
+        <v>57</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="M63" s="10">
+        <v>46094.652777777781</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>40</v>
       </c>
@@ -5107,8 +6348,17 @@
       <c r="H64" s="10">
         <v>46093.919444444444</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K64" s="4">
+        <v>58</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="M64" s="10">
+        <v>46094.652777777781</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>41</v>
       </c>
@@ -5127,8 +6377,17 @@
       <c r="H65" s="10">
         <v>46093.915972222225</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K65" s="4">
+        <v>59</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="M65" s="10">
+        <v>46094.645138888889</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>42</v>
       </c>
@@ -5147,8 +6406,17 @@
       <c r="H66" s="10">
         <v>46093.912499999999</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K66" s="4">
+        <v>60</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="M66" s="10">
+        <v>46094.644444444442</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>43</v>
       </c>
@@ -5167,8 +6435,17 @@
       <c r="H67" s="10">
         <v>46093.910416666666</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K67" s="3">
+        <v>61</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="M67" s="10">
+        <v>46094.643055555556</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>44</v>
       </c>
@@ -5187,8 +6464,17 @@
       <c r="H68" s="10">
         <v>46093.90902777778</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K68" s="4">
+        <v>62</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="M68" s="10">
+        <v>46094.642361111109</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>45</v>
       </c>
@@ -5207,8 +6493,17 @@
       <c r="H69" s="10">
         <v>46093.90625</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K69" s="4">
+        <v>63</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="M69" s="10">
+        <v>46094.64166666667</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>46</v>
       </c>
@@ -5227,8 +6522,17 @@
       <c r="H70" s="10">
         <v>46093.90625</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K70" s="4">
+        <v>64</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="M70" s="10">
+        <v>46094.63958333333</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>47</v>
       </c>
@@ -5247,8 +6551,17 @@
       <c r="H71" s="10">
         <v>46093.899305555555</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K71" s="4">
+        <v>65</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M71" s="10">
+        <v>46094.638888888891</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>48</v>
       </c>
@@ -5267,8 +6580,17 @@
       <c r="H72" s="10">
         <v>46093.897222222222</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K72" s="4">
+        <v>66</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="M72" s="10">
+        <v>46094.637499999997</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>49</v>
       </c>
@@ -5287,8 +6609,17 @@
       <c r="H73" s="10">
         <v>46093.897222222222</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K73" s="4">
+        <v>67</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M73" s="10">
+        <v>46094.635416666664</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>50</v>
       </c>
@@ -5307,8 +6638,17 @@
       <c r="H74" s="10">
         <v>46093.895138888889</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K74" s="4">
+        <v>68</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="M74" s="10">
+        <v>46094.62777777778</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>51</v>
       </c>
@@ -5327,8 +6667,17 @@
       <c r="H75" s="10">
         <v>46093.893750000003</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K75" s="4">
+        <v>69</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="M75" s="10">
+        <v>46094.622916666667</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>52</v>
       </c>
@@ -5347,8 +6696,17 @@
       <c r="H76" s="10">
         <v>46093.892361111109</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K76" s="4">
+        <v>70</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="M76" s="10">
+        <v>46094.618750000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>53</v>
       </c>
@@ -5367,8 +6725,17 @@
       <c r="H77" s="10">
         <v>46093.89166666667</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K77" s="4">
+        <v>71</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M77" s="10">
+        <v>46094.615277777775</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>54</v>
       </c>
@@ -5387,8 +6754,17 @@
       <c r="H78" s="10">
         <v>46093.890972222223</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K78" s="4">
+        <v>72</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="M78" s="10">
+        <v>46094.61041666667</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>55</v>
       </c>
@@ -5407,8 +6783,17 @@
       <c r="H79" s="10">
         <v>46093.890972222223</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K79" s="3">
+        <v>73</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="M79" s="10">
+        <v>46094.609027777777</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>56</v>
       </c>
@@ -5427,8 +6812,17 @@
       <c r="H80" s="10">
         <v>46093.890277777777</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K80" s="4">
+        <v>74</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="M80" s="10">
+        <v>46094.605555555558</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>57</v>
       </c>
@@ -5447,8 +6841,17 @@
       <c r="H81" s="10">
         <v>46093.888194444444</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K81" s="4">
+        <v>75</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="M81" s="10">
+        <v>46094.604861111111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>58</v>
       </c>
@@ -5467,8 +6870,17 @@
       <c r="H82" s="10">
         <v>46093.886111111111</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K82" s="4">
+        <v>76</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="M82" s="10">
+        <v>46094.604166666664</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>59</v>
       </c>
@@ -5487,8 +6899,17 @@
       <c r="H83" s="10">
         <v>46093.884722222225</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K83" s="4">
+        <v>77</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M83" s="10">
+        <v>46094.601388888892</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>60</v>
       </c>
@@ -5507,8 +6928,17 @@
       <c r="H84" s="10">
         <v>46093.884722222225</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K84" s="4">
+        <v>78</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="M84" s="10">
+        <v>46094.601388888892</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>61</v>
       </c>
@@ -5527,8 +6957,17 @@
       <c r="H85" s="10">
         <v>46093.883333333331</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K85" s="4">
+        <v>79</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="M85" s="10">
+        <v>46094.599305555559</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>62</v>
       </c>
@@ -5547,8 +6986,17 @@
       <c r="H86" s="10">
         <v>46093.881944444445</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K86" s="4">
+        <v>80</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="M86" s="10">
+        <v>46094.59652777778</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>63</v>
       </c>
@@ -5567,8 +7015,17 @@
       <c r="H87" s="10">
         <v>46093.881249999999</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K87" s="4">
+        <v>81</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M87" s="10">
+        <v>46094.594444444447</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>64</v>
       </c>
@@ -5587,8 +7044,17 @@
       <c r="H88" s="10">
         <v>46093.880555555559</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K88" s="4">
+        <v>82</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="M88" s="10">
+        <v>46094.593055555553</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>65</v>
       </c>
@@ -5607,8 +7073,17 @@
       <c r="H89" s="10">
         <v>46093.878472222219</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K89" s="4">
+        <v>83</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="M89" s="10">
+        <v>46094.592361111114</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>66</v>
       </c>
@@ -5627,8 +7102,17 @@
       <c r="H90" s="10">
         <v>46093.87777777778</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K90" s="4">
+        <v>84</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="M90" s="10">
+        <v>46094.591666666667</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>67</v>
       </c>
@@ -5647,8 +7131,17 @@
       <c r="H91" s="10">
         <v>46093.877083333333</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K91" s="3">
+        <v>85</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="M91" s="10">
+        <v>46094.591666666667</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>68</v>
       </c>
@@ -5667,8 +7160,17 @@
       <c r="H92" s="10">
         <v>46093.873611111114</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K92" s="4">
+        <v>86</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="M92" s="10">
+        <v>46094.59097222222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>69</v>
       </c>
@@ -5687,8 +7189,17 @@
       <c r="H93" s="10">
         <v>46093.872916666667</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K93" s="4">
+        <v>87</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="M93" s="10">
+        <v>46094.590277777781</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>70</v>
       </c>
@@ -5707,8 +7218,17 @@
       <c r="H94" s="10">
         <v>46093.867361111108</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K94" s="4">
+        <v>88</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="M94" s="10">
+        <v>46094.587500000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>71</v>
       </c>
@@ -5727,8 +7247,17 @@
       <c r="H95" s="10">
         <v>46093.863888888889</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K95" s="4">
+        <v>89</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="M95" s="10">
+        <v>46094.585416666669</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>72</v>
       </c>
@@ -5747,8 +7276,17 @@
       <c r="H96" s="10">
         <v>46093.859722222223</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K96" s="4">
+        <v>90</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="M96" s="10">
+        <v>46094.585416666669</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>73</v>
       </c>
@@ -5767,8 +7305,17 @@
       <c r="H97" s="10">
         <v>46093.855555555558</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K97" s="4">
+        <v>91</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="M97" s="10">
+        <v>46094.584722222222</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>74</v>
       </c>
@@ -5787,8 +7334,17 @@
       <c r="H98" s="10">
         <v>46093.852083333331</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K98" s="4">
+        <v>92</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="M98" s="10">
+        <v>46094.581944444442</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>75</v>
       </c>
@@ -5807,8 +7363,17 @@
       <c r="H99" s="10">
         <v>46093.828472222223</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K99" s="4">
+        <v>93</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="M99" s="10">
+        <v>46094.581944444442</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>76</v>
       </c>
@@ -5827,8 +7392,17 @@
       <c r="H100" s="10">
         <v>46093.826388888891</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K100" s="4">
+        <v>94</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="M100" s="10">
+        <v>46094.578472222223</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>77</v>
       </c>
@@ -5847,8 +7421,17 @@
       <c r="H101" s="10">
         <v>46093.824999999997</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K101" s="4">
+        <v>95</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="M101" s="10">
+        <v>46094.57708333333</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>78</v>
       </c>
@@ -5867,8 +7450,17 @@
       <c r="H102" s="10">
         <v>46093.818055555559</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K102" s="4">
+        <v>96</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="M102" s="10">
+        <v>46094.575694444444</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>79</v>
       </c>
@@ -5887,8 +7479,17 @@
       <c r="H103" s="10">
         <v>46093.814583333333</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K103" s="3">
+        <v>97</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="M103" s="10">
+        <v>46094.574305555558</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>80</v>
       </c>
@@ -5907,8 +7508,17 @@
       <c r="H104" s="10">
         <v>46093.8</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K104" s="4">
+        <v>98</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="M104" s="10">
+        <v>46094.572222222225</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>81</v>
       </c>
@@ -5927,8 +7537,17 @@
       <c r="H105" s="10">
         <v>46093.769444444442</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K105" s="4">
+        <v>99</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="M105" s="10">
+        <v>46094.570833333331</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>82</v>
       </c>
@@ -5947,8 +7566,17 @@
       <c r="H106" s="10">
         <v>46093.768055555556</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K106" s="4">
+        <v>100</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="M106" s="10">
+        <v>46094.570833333331</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>83</v>
       </c>
@@ -5967,8 +7595,17 @@
       <c r="H107" s="10">
         <v>46093.759722222225</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K107" s="4">
+        <v>101</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="M107" s="10">
+        <v>46094.570138888892</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>84</v>
       </c>
@@ -5987,8 +7624,17 @@
       <c r="H108" s="10">
         <v>46093.758333333331</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K108" s="4">
+        <v>102</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M108" s="10">
+        <v>46094.568055555559</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>85</v>
       </c>
@@ -6007,8 +7653,17 @@
       <c r="H109" s="10">
         <v>46093.754166666666</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K109" s="4">
+        <v>103</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="M109" s="10">
+        <v>46094.565972222219</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>86</v>
       </c>
@@ -6027,8 +7682,17 @@
       <c r="H110" s="10">
         <v>46093.75</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K110" s="4">
+        <v>104</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M110" s="10">
+        <v>46094.565972222219</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>87</v>
       </c>
@@ -6047,8 +7711,17 @@
       <c r="H111" s="10">
         <v>46093.744444444441</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K111" s="4">
+        <v>105</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="M111" s="10">
+        <v>46094.563194444447</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>88</v>
       </c>
@@ -6067,8 +7740,17 @@
       <c r="H112" s="10">
         <v>46093.742361111108</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K112" s="4">
+        <v>106</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M112" s="10">
+        <v>46094.560416666667</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>89</v>
       </c>
@@ -6087,8 +7769,17 @@
       <c r="H113" s="10">
         <v>46093.740972222222</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K113" s="4">
+        <v>107</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="M113" s="10">
+        <v>46094.559027777781</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>90</v>
       </c>
@@ -6107,8 +7798,17 @@
       <c r="H114" s="10">
         <v>46093.740277777775</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K114" s="4">
+        <v>108</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="M114" s="10">
+        <v>46094.556944444441</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>91</v>
       </c>
@@ -6127,8 +7827,17 @@
       <c r="H115" s="10">
         <v>46093.740277777775</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K115" s="3">
+        <v>109</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="M115" s="10">
+        <v>46094.556944444441</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>92</v>
       </c>
@@ -6147,8 +7856,17 @@
       <c r="H116" s="10">
         <v>46093.738888888889</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K116" s="4">
+        <v>110</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="M116" s="10">
+        <v>46094.552777777775</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>93</v>
       </c>
@@ -6167,8 +7885,17 @@
       <c r="H117" s="10">
         <v>46093.738888888889</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K117" s="4">
+        <v>111</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="M117" s="10">
+        <v>46094.550694444442</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>94</v>
       </c>
@@ -6187,8 +7914,17 @@
       <c r="H118" s="10">
         <v>46093.731944444444</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K118" s="4">
+        <v>112</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="M118" s="10">
+        <v>46094.549305555556</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>95</v>
       </c>
@@ -6207,8 +7943,17 @@
       <c r="H119" s="10">
         <v>46093.731944444444</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K119" s="4">
+        <v>113</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="M119" s="10">
+        <v>46094.54791666667</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>96</v>
       </c>
@@ -6227,8 +7972,17 @@
       <c r="H120" s="10">
         <v>46093.731249999997</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K120" s="4">
+        <v>114</v>
+      </c>
+      <c r="L120" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="M120" s="10">
+        <v>46094.547222222223</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>97</v>
       </c>
@@ -6247,8 +8001,17 @@
       <c r="H121" s="10">
         <v>46093.730555555558</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K121" s="4">
+        <v>115</v>
+      </c>
+      <c r="L121" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="M121" s="10">
+        <v>46094.546527777777</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>98</v>
       </c>
@@ -6267,8 +8030,17 @@
       <c r="H122" s="10">
         <v>46093.728472222225</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K122" s="4">
+        <v>116</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="M122" s="10">
+        <v>46094.545138888891</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>99</v>
       </c>
@@ -6287,8 +8059,17 @@
       <c r="H123" s="10">
         <v>46093.727777777778</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K123" s="4">
+        <v>117</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="M123" s="10">
+        <v>46094.544444444444</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>100</v>
       </c>
@@ -6307,8 +8088,17 @@
       <c r="H124" s="10">
         <v>46093.727083333331</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K124" s="4">
+        <v>118</v>
+      </c>
+      <c r="L124" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="M124" s="10">
+        <v>46094.544444444444</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>101</v>
       </c>
@@ -6327,8 +8117,17 @@
       <c r="H125" s="10">
         <v>46093.726388888892</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K125" s="4">
+        <v>119</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="M125" s="10">
+        <v>46094.543055555558</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>102</v>
       </c>
@@ -6347,8 +8146,17 @@
       <c r="H126" s="10">
         <v>46093.724305555559</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K126" s="4">
+        <v>120</v>
+      </c>
+      <c r="L126" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="M126" s="10">
+        <v>46094.543055555558</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>103</v>
       </c>
@@ -6367,8 +8175,17 @@
       <c r="H127" s="10">
         <v>46093.723611111112</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K127" s="3">
+        <v>121</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="M127" s="10">
+        <v>46094.542361111111</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>104</v>
       </c>
@@ -6387,8 +8204,17 @@
       <c r="H128" s="10">
         <v>46093.723611111112</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K128" s="4">
+        <v>122</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="M128" s="10">
+        <v>46094.540972222225</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>105</v>
       </c>
@@ -6407,8 +8233,17 @@
       <c r="H129" s="10">
         <v>46093.722222222219</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K129" s="4">
+        <v>123</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="M129" s="10">
+        <v>46094.539583333331</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>106</v>
       </c>
@@ -6427,8 +8262,17 @@
       <c r="H130" s="10">
         <v>46093.722222222219</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K130" s="4">
+        <v>124</v>
+      </c>
+      <c r="L130" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="M130" s="10">
+        <v>46094.538888888892</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>107</v>
       </c>
@@ -6447,8 +8291,17 @@
       <c r="H131" s="10">
         <v>46093.72152777778</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K131" s="4">
+        <v>125</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="M131" s="10">
+        <v>46094.538888888892</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>108</v>
       </c>
@@ -6467,8 +8320,17 @@
       <c r="H132" s="10">
         <v>46093.720833333333</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K132" s="4">
+        <v>126</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="M132" s="10">
+        <v>46094.538194444445</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>109</v>
       </c>
@@ -6487,8 +8349,17 @@
       <c r="H133" s="10">
         <v>46093.720138888886</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K133" s="4">
+        <v>127</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="M133" s="10">
+        <v>46094.538194444445</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>110</v>
       </c>
@@ -6507,8 +8378,17 @@
       <c r="H134" s="10">
         <v>46093.718055555553</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K134" s="4">
+        <v>128</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="M134" s="10">
+        <v>46094.537499999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>111</v>
       </c>
@@ -6527,8 +8407,17 @@
       <c r="H135" s="10">
         <v>46093.71597222222</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K135" s="4">
+        <v>129</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="M135" s="10">
+        <v>46094.536805555559</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>112</v>
       </c>
@@ -6547,8 +8436,17 @@
       <c r="H136" s="10">
         <v>46093.714583333334</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K136" s="4">
+        <v>130</v>
+      </c>
+      <c r="L136" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="M136" s="10">
+        <v>46094.535416666666</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>113</v>
       </c>
@@ -6567,8 +8465,17 @@
       <c r="H137" s="10">
         <v>46093.713888888888</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K137" s="4">
+        <v>131</v>
+      </c>
+      <c r="L137" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="M137" s="10">
+        <v>46094.533333333333</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>114</v>
       </c>
@@ -6587,8 +8494,17 @@
       <c r="H138" s="10">
         <v>46093.712500000001</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K138" s="4">
+        <v>132</v>
+      </c>
+      <c r="L138" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M138" s="10">
+        <v>46094.533333333333</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>115</v>
       </c>
@@ -6607,8 +8523,17 @@
       <c r="H139" s="10">
         <v>46093.712500000001</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K139" s="3">
+        <v>133</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="M139" s="10">
+        <v>46094.532638888886</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>116</v>
       </c>
@@ -6627,8 +8552,17 @@
       <c r="H140" s="10">
         <v>46093.711111111108</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K140" s="4">
+        <v>134</v>
+      </c>
+      <c r="L140" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M140" s="10">
+        <v>46094.53125</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>117</v>
       </c>
@@ -6647,8 +8581,17 @@
       <c r="H141" s="10">
         <v>46093.709722222222</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K141" s="4">
+        <v>135</v>
+      </c>
+      <c r="L141" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="M141" s="10">
+        <v>46094.53125</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>118</v>
       </c>
@@ -6667,8 +8610,17 @@
       <c r="H142" s="10">
         <v>46093.706944444442</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K142" s="4">
+        <v>136</v>
+      </c>
+      <c r="L142" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="M142" s="10">
+        <v>46094.529166666667</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>119</v>
       </c>
@@ -6687,8 +8639,17 @@
       <c r="H143" s="10">
         <v>46093.706250000003</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K143" s="4">
+        <v>137</v>
+      </c>
+      <c r="L143" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="M143" s="10">
+        <v>46094.52847222222</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>120</v>
       </c>
@@ -6707,8 +8668,17 @@
       <c r="H144" s="10">
         <v>46093.706250000003</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K144" s="4">
+        <v>138</v>
+      </c>
+      <c r="L144" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M144" s="10">
+        <v>46094.527083333334</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>121</v>
       </c>
@@ -6727,8 +8697,17 @@
       <c r="H145" s="10">
         <v>46093.706250000003</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K145" s="4">
+        <v>139</v>
+      </c>
+      <c r="L145" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="M145" s="10">
+        <v>46094.525694444441</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>122</v>
       </c>
@@ -6747,8 +8726,17 @@
       <c r="H146" s="10">
         <v>46093.705555555556</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K146" s="4">
+        <v>140</v>
+      </c>
+      <c r="L146" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="M146" s="10">
+        <v>46094.525000000001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>123</v>
       </c>
@@ -6767,8 +8755,17 @@
       <c r="H147" s="10">
         <v>46093.705555555556</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K147" s="4">
+        <v>141</v>
+      </c>
+      <c r="L147" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="M147" s="10">
+        <v>46094.522916666669</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>124</v>
       </c>
@@ -6787,8 +8784,17 @@
       <c r="H148" s="10">
         <v>46093.705555555556</v>
       </c>
-    </row>
-    <row r="149" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K148" s="4">
+        <v>142</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="M148" s="10">
+        <v>46094.520833333336</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>125</v>
       </c>
@@ -6807,8 +8813,17 @@
       <c r="H149" s="10">
         <v>46093.704861111109</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K149" s="4">
+        <v>143</v>
+      </c>
+      <c r="L149" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="M149" s="10">
+        <v>46094.520138888889</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>126</v>
       </c>
@@ -6827,8 +8842,17 @@
       <c r="H150" s="10">
         <v>46093.70208333333</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K150" s="4">
+        <v>144</v>
+      </c>
+      <c r="L150" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="M150" s="10">
+        <v>46094.515277777777</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>127</v>
       </c>
@@ -6847,8 +8871,17 @@
       <c r="H151" s="10">
         <v>46093.70208333333</v>
       </c>
-    </row>
-    <row r="152" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K151" s="3">
+        <v>145</v>
+      </c>
+      <c r="L151" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="M151" s="10">
+        <v>46094.51458333333</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>128</v>
       </c>
@@ -6867,8 +8900,17 @@
       <c r="H152" s="10">
         <v>46093.701388888891</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K152" s="4">
+        <v>146</v>
+      </c>
+      <c r="L152" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="M152" s="10">
+        <v>46094.513888888891</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>129</v>
       </c>
@@ -6887,8 +8929,17 @@
       <c r="H153" s="10">
         <v>46093.701388888891</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K153" s="4">
+        <v>147</v>
+      </c>
+      <c r="L153" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M153" s="10">
+        <v>46094.513888888891</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>130</v>
       </c>
@@ -6907,8 +8958,17 @@
       <c r="H154" s="10">
         <v>46093.699305555558</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K154" s="4">
+        <v>148</v>
+      </c>
+      <c r="L154" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="M154" s="10">
+        <v>46094.513194444444</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>131</v>
       </c>
@@ -6927,8 +8987,17 @@
       <c r="H155" s="10">
         <v>46093.698611111111</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K155" s="4">
+        <v>149</v>
+      </c>
+      <c r="L155" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="M155" s="10">
+        <v>46094.511805555558</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>132</v>
       </c>
@@ -6947,8 +9016,17 @@
       <c r="H156" s="10">
         <v>46093.697916666664</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K156" s="4">
+        <v>150</v>
+      </c>
+      <c r="L156" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="M156" s="10">
+        <v>46094.511111111111</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>133</v>
       </c>
@@ -6967,8 +9045,17 @@
       <c r="H157" s="10">
         <v>46093.697222222225</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K157" s="4">
+        <v>151</v>
+      </c>
+      <c r="L157" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="M157" s="10">
+        <v>46094.510416666664</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>134</v>
       </c>
@@ -6987,8 +9074,17 @@
       <c r="H158" s="10">
         <v>46093.695833333331</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K158" s="4">
+        <v>152</v>
+      </c>
+      <c r="L158" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M158" s="10">
+        <v>46094.509722222225</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>135</v>
       </c>
@@ -7007,8 +9103,17 @@
       <c r="H159" s="10">
         <v>46093.695833333331</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K159" s="4">
+        <v>153</v>
+      </c>
+      <c r="L159" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="M159" s="10">
+        <v>46094.508333333331</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>136</v>
       </c>
@@ -7027,8 +9132,17 @@
       <c r="H160" s="10">
         <v>46093.693749999999</v>
       </c>
-    </row>
-    <row r="161" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K160" s="4">
+        <v>154</v>
+      </c>
+      <c r="L160" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="M160" s="10">
+        <v>46094.506249999999</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>137</v>
       </c>
@@ -7047,8 +9161,17 @@
       <c r="H161" s="10">
         <v>46093.693749999999</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K161" s="4">
+        <v>155</v>
+      </c>
+      <c r="L161" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="M161" s="10">
+        <v>46094.504861111112</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>138</v>
       </c>
@@ -7067,8 +9190,17 @@
       <c r="H162" s="10">
         <v>46093.691666666666</v>
       </c>
-    </row>
-    <row r="163" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K162" s="4">
+        <v>156</v>
+      </c>
+      <c r="L162" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="M162" s="10">
+        <v>46094.503472222219</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>139</v>
       </c>
@@ -7087,8 +9219,17 @@
       <c r="H163" s="10">
         <v>46093.691666666666</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K163" s="3">
+        <v>157</v>
+      </c>
+      <c r="L163" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="M163" s="10">
+        <v>46094.50277777778</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>140</v>
       </c>
@@ -7107,8 +9248,17 @@
       <c r="H164" s="10">
         <v>46093.69027777778</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K164" s="4">
+        <v>158</v>
+      </c>
+      <c r="L164" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="M164" s="10">
+        <v>46094.50277777778</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>141</v>
       </c>
@@ -7127,8 +9277,17 @@
       <c r="H165" s="10">
         <v>46093.69027777778</v>
       </c>
-    </row>
-    <row r="166" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K165" s="4">
+        <v>159</v>
+      </c>
+      <c r="L165" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="M165" s="10">
+        <v>46094.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>142</v>
       </c>
@@ -7147,8 +9306,17 @@
       <c r="H166" s="10">
         <v>46093.689583333333</v>
       </c>
-    </row>
-    <row r="167" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K166" s="4">
+        <v>160</v>
+      </c>
+      <c r="L166" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="M166" s="10">
+        <v>46094.494444444441</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>143</v>
       </c>
@@ -7167,8 +9335,17 @@
       <c r="H167" s="10">
         <v>46093.688194444447</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K167" s="4">
+        <v>161</v>
+      </c>
+      <c r="L167" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="M167" s="10">
+        <v>46094.493055555555</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>144</v>
       </c>
@@ -7187,8 +9364,17 @@
       <c r="H168" s="10">
         <v>46093.6875</v>
       </c>
-    </row>
-    <row r="169" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K168" s="4">
+        <v>162</v>
+      </c>
+      <c r="L168" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="M168" s="10">
+        <v>46094.490972222222</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>145</v>
       </c>
@@ -7207,8 +9393,17 @@
       <c r="H169" s="10">
         <v>46093.686111111114</v>
       </c>
-    </row>
-    <row r="170" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K169" s="4">
+        <v>163</v>
+      </c>
+      <c r="L169" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="M169" s="10">
+        <v>46094.490972222222</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>146</v>
       </c>
@@ -7227,8 +9422,17 @@
       <c r="H170" s="10">
         <v>46093.683333333334</v>
       </c>
-    </row>
-    <row r="171" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K170" s="4">
+        <v>164</v>
+      </c>
+      <c r="L170" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="M170" s="10">
+        <v>46094.490277777775</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>147</v>
       </c>
@@ -7247,8 +9451,17 @@
       <c r="H171" s="10">
         <v>46093.682638888888</v>
       </c>
-    </row>
-    <row r="172" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K171" s="4">
+        <v>165</v>
+      </c>
+      <c r="L171" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="M171" s="10">
+        <v>46094.486111111109</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>148</v>
       </c>
@@ -7267,8 +9480,17 @@
       <c r="H172" s="10">
         <v>46093.679861111108</v>
       </c>
-    </row>
-    <row r="173" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K172" s="4">
+        <v>166</v>
+      </c>
+      <c r="L172" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M172" s="10">
+        <v>46094.48541666667</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>149</v>
       </c>
@@ -7287,8 +9509,17 @@
       <c r="H173" s="10">
         <v>46093.679861111108</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K173" s="4">
+        <v>167</v>
+      </c>
+      <c r="L173" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="M173" s="10">
+        <v>46094.48333333333</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>150</v>
       </c>
@@ -7307,8 +9538,17 @@
       <c r="H174" s="10">
         <v>46093.673611111109</v>
       </c>
-    </row>
-    <row r="175" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K174" s="4">
+        <v>168</v>
+      </c>
+      <c r="L174" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="M174" s="10">
+        <v>46094.478472222225</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>151</v>
       </c>
@@ -7327,8 +9567,17 @@
       <c r="H175" s="10">
         <v>46093.670138888891</v>
       </c>
-    </row>
-    <row r="176" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K175" s="3">
+        <v>169</v>
+      </c>
+      <c r="L175" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="M175" s="10">
+        <v>46094.477777777778</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>152</v>
       </c>
@@ -7347,8 +9596,17 @@
       <c r="H176" s="10">
         <v>46093.669444444444</v>
       </c>
-    </row>
-    <row r="177" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K176" s="4">
+        <v>170</v>
+      </c>
+      <c r="L176" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="M176" s="10">
+        <v>46094.477083333331</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>153</v>
       </c>
@@ -7367,8 +9625,17 @@
       <c r="H177" s="10">
         <v>46093.668749999997</v>
       </c>
-    </row>
-    <row r="178" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K177" s="4">
+        <v>171</v>
+      </c>
+      <c r="L177" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="M177" s="10">
+        <v>46094.474305555559</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>154</v>
       </c>
@@ -7387,8 +9654,17 @@
       <c r="H178" s="10">
         <v>46093.668055555558</v>
       </c>
-    </row>
-    <row r="179" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K178" s="4">
+        <v>172</v>
+      </c>
+      <c r="L178" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="M178" s="10">
+        <v>46094.473611111112</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>155</v>
       </c>
@@ -7407,8 +9683,17 @@
       <c r="H179" s="10">
         <v>46093.667361111111</v>
       </c>
-    </row>
-    <row r="180" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K179" s="4">
+        <v>173</v>
+      </c>
+      <c r="L179" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="M179" s="10">
+        <v>46094.472916666666</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>156</v>
       </c>
@@ -7427,8 +9712,17 @@
       <c r="H180" s="10">
         <v>46093.667361111111</v>
       </c>
-    </row>
-    <row r="181" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K180" s="4">
+        <v>174</v>
+      </c>
+      <c r="L180" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="M180" s="10">
+        <v>46094.472222222219</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>157</v>
       </c>
@@ -7447,8 +9741,17 @@
       <c r="H181" s="10">
         <v>46093.666666666664</v>
       </c>
-    </row>
-    <row r="182" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K181" s="4">
+        <v>175</v>
+      </c>
+      <c r="L181" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="M181" s="10">
+        <v>46094.47152777778</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
         <v>158</v>
       </c>
@@ -7467,8 +9770,17 @@
       <c r="H182" s="10">
         <v>46093.665277777778</v>
       </c>
-    </row>
-    <row r="183" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K182" s="4">
+        <v>176</v>
+      </c>
+      <c r="L182" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="M182" s="10">
+        <v>46094.47152777778</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>159</v>
       </c>
@@ -7487,8 +9799,17 @@
       <c r="H183" s="10">
         <v>46093.665277777778</v>
       </c>
-    </row>
-    <row r="184" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K183" s="4">
+        <v>177</v>
+      </c>
+      <c r="L183" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="M183" s="10">
+        <v>46094.468055555553</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>160</v>
       </c>
@@ -7507,8 +9828,17 @@
       <c r="H184" s="10">
         <v>46093.665277777778</v>
       </c>
-    </row>
-    <row r="185" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K184" s="4">
+        <v>178</v>
+      </c>
+      <c r="L184" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="M184" s="10">
+        <v>46094.465277777781</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>161</v>
       </c>
@@ -7527,8 +9857,17 @@
       <c r="H185" s="10">
         <v>46093.664583333331</v>
       </c>
-    </row>
-    <row r="186" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K185" s="4">
+        <v>179</v>
+      </c>
+      <c r="L185" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="M185" s="10">
+        <v>46094.464583333334</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>162</v>
       </c>
@@ -7547,8 +9886,17 @@
       <c r="H186" s="10">
         <v>46093.664583333331</v>
       </c>
-    </row>
-    <row r="187" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K186" s="4">
+        <v>180</v>
+      </c>
+      <c r="L186" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="M186" s="10">
+        <v>46094.463888888888</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>163</v>
       </c>
@@ -7567,8 +9915,17 @@
       <c r="H187" s="10">
         <v>46093.663888888892</v>
       </c>
-    </row>
-    <row r="188" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K187" s="3">
+        <v>181</v>
+      </c>
+      <c r="L187" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="M187" s="10">
+        <v>46094.462500000001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>164</v>
       </c>
@@ -7587,8 +9944,17 @@
       <c r="H188" s="10">
         <v>46093.661805555559</v>
       </c>
-    </row>
-    <row r="189" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K188" s="4">
+        <v>182</v>
+      </c>
+      <c r="L188" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="M188" s="10">
+        <v>46094.461805555555</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>165</v>
       </c>
@@ -7607,8 +9973,17 @@
       <c r="H189" s="10">
         <v>46093.661111111112</v>
       </c>
-    </row>
-    <row r="190" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K189" s="4">
+        <v>183</v>
+      </c>
+      <c r="L189" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="M189" s="10">
+        <v>46094.461805555555</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>166</v>
       </c>
@@ -7627,8 +10002,17 @@
       <c r="H190" s="10">
         <v>46093.659722222219</v>
       </c>
-    </row>
-    <row r="191" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K190" s="4">
+        <v>184</v>
+      </c>
+      <c r="L190" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="M190" s="10">
+        <v>46094.459027777775</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>167</v>
       </c>
@@ -7647,8 +10031,17 @@
       <c r="H191" s="10">
         <v>46093.657638888886</v>
       </c>
-    </row>
-    <row r="192" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K191" s="4">
+        <v>185</v>
+      </c>
+      <c r="L191" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="M191" s="10">
+        <v>46094.458333333336</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>168</v>
       </c>
@@ -7667,8 +10060,17 @@
       <c r="H192" s="10">
         <v>46093.656944444447</v>
       </c>
-    </row>
-    <row r="193" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K192" s="4">
+        <v>186</v>
+      </c>
+      <c r="L192" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M192" s="10">
+        <v>46094.457638888889</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>169</v>
       </c>
@@ -7687,8 +10089,17 @@
       <c r="H193" s="10">
         <v>46093.655555555553</v>
       </c>
-    </row>
-    <row r="194" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K193" s="4">
+        <v>187</v>
+      </c>
+      <c r="L193" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M193" s="10">
+        <v>46094.456944444442</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>170</v>
       </c>
@@ -7707,8 +10118,17 @@
       <c r="H194" s="10">
         <v>46093.654861111114</v>
       </c>
-    </row>
-    <row r="195" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K194" s="4">
+        <v>188</v>
+      </c>
+      <c r="L194" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M194" s="10">
+        <v>46094.456250000003</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>171</v>
       </c>
@@ -7727,8 +10147,17 @@
       <c r="H195" s="10">
         <v>46093.654861111114</v>
       </c>
-    </row>
-    <row r="196" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K195" s="4">
+        <v>189</v>
+      </c>
+      <c r="L195" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M195" s="10">
+        <v>46094.454861111109</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>172</v>
       </c>
@@ -7747,8 +10176,17 @@
       <c r="H196" s="10">
         <v>46093.654166666667</v>
       </c>
-    </row>
-    <row r="197" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K196" s="4">
+        <v>190</v>
+      </c>
+      <c r="L196" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M196" s="10">
+        <v>46094.452777777777</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>173</v>
       </c>
@@ -7767,8 +10205,17 @@
       <c r="H197" s="10">
         <v>46093.652777777781</v>
       </c>
-    </row>
-    <row r="198" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K197" s="4">
+        <v>191</v>
+      </c>
+      <c r="L197" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="M197" s="10">
+        <v>46094.45208333333</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>174</v>
       </c>
@@ -7787,8 +10234,17 @@
       <c r="H198" s="10">
         <v>46093.652777777781</v>
       </c>
-    </row>
-    <row r="199" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K198" s="4">
+        <v>192</v>
+      </c>
+      <c r="L198" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="M198" s="10">
+        <v>46094.451388888891</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>175</v>
       </c>
@@ -7807,8 +10263,17 @@
       <c r="H199" s="10">
         <v>46093.652083333334</v>
       </c>
-    </row>
-    <row r="200" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K199" s="3">
+        <v>193</v>
+      </c>
+      <c r="L199" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="M199" s="10">
+        <v>46094.449305555558</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>176</v>
       </c>
@@ -7827,8 +10292,17 @@
       <c r="H200" s="10">
         <v>46093.651388888888</v>
       </c>
-    </row>
-    <row r="201" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K200" s="4">
+        <v>194</v>
+      </c>
+      <c r="L200" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="M200" s="10">
+        <v>46094.449305555558</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>177</v>
       </c>
@@ -7847,8 +10321,17 @@
       <c r="H201" s="10">
         <v>46093.650694444441</v>
       </c>
-    </row>
-    <row r="202" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K201" s="4">
+        <v>195</v>
+      </c>
+      <c r="L201" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="M201" s="10">
+        <v>46094.447222222225</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>178</v>
       </c>
@@ -7867,8 +10350,17 @@
       <c r="H202" s="10">
         <v>46093.65</v>
       </c>
-    </row>
-    <row r="203" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K202" s="4">
+        <v>196</v>
+      </c>
+      <c r="L202" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="M202" s="10">
+        <v>46094.446527777778</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>179</v>
       </c>
@@ -7887,8 +10379,17 @@
       <c r="H203" s="10">
         <v>46093.65</v>
       </c>
-    </row>
-    <row r="204" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K203" s="4">
+        <v>197</v>
+      </c>
+      <c r="L203" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="M203" s="10">
+        <v>46094.445138888892</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
         <v>180</v>
       </c>
@@ -7907,8 +10408,17 @@
       <c r="H204" s="10">
         <v>46093.649305555555</v>
       </c>
-    </row>
-    <row r="205" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K204" s="4">
+        <v>198</v>
+      </c>
+      <c r="L204" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="M204" s="10">
+        <v>46094.443055555559</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>181</v>
       </c>
@@ -7927,8 +10437,17 @@
       <c r="H205" s="10">
         <v>46093.649305555555</v>
       </c>
-    </row>
-    <row r="206" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K205" s="4">
+        <v>199</v>
+      </c>
+      <c r="L205" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="M205" s="10">
+        <v>46094.442361111112</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>182</v>
       </c>
@@ -7947,8 +10466,17 @@
       <c r="H206" s="10">
         <v>46093.647916666669</v>
       </c>
-    </row>
-    <row r="207" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K206" s="4">
+        <v>200</v>
+      </c>
+      <c r="L206" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="M206" s="10">
+        <v>46094.440972222219</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>183</v>
       </c>
@@ -7967,8 +10495,17 @@
       <c r="H207" s="10">
         <v>46093.647222222222</v>
       </c>
-    </row>
-    <row r="208" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K207" s="4">
+        <v>201</v>
+      </c>
+      <c r="L207" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="M207" s="10">
+        <v>46094.44027777778</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>184</v>
       </c>
@@ -7987,8 +10524,17 @@
       <c r="H208" s="10">
         <v>46093.647222222222</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K208" s="4">
+        <v>202</v>
+      </c>
+      <c r="L208" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="M208" s="10">
+        <v>46094.44027777778</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>185</v>
       </c>
@@ -7998,8 +10544,17 @@
       <c r="C209" s="5">
         <v>46092.780555555553</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K209" s="4">
+        <v>203</v>
+      </c>
+      <c r="L209" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="M209" s="10">
+        <v>46094.438888888886</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>186</v>
       </c>
@@ -8009,8 +10564,17 @@
       <c r="C210" s="5">
         <v>46092.780555555553</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K210" s="4">
+        <v>204</v>
+      </c>
+      <c r="L210" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="M210" s="10">
+        <v>46094.4375</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>187</v>
       </c>
@@ -8020,8 +10584,17 @@
       <c r="C211" s="5">
         <v>46092.779861111114</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K211" s="3">
+        <v>205</v>
+      </c>
+      <c r="L211" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="M211" s="10">
+        <v>46094.435416666667</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>188</v>
       </c>
@@ -8031,8 +10604,17 @@
       <c r="C212" s="5">
         <v>46092.779861111114</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K212" s="4">
+        <v>206</v>
+      </c>
+      <c r="L212" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M212" s="10">
+        <v>46094.434027777781</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>189</v>
       </c>
@@ -8042,8 +10624,17 @@
       <c r="C213" s="5">
         <v>46092.779861111114</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K213" s="4">
+        <v>207</v>
+      </c>
+      <c r="L213" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="M213" s="10">
+        <v>46094.433333333334</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>190</v>
       </c>
@@ -8053,8 +10644,17 @@
       <c r="C214" s="5">
         <v>46092.779861111114</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K214" s="4">
+        <v>208</v>
+      </c>
+      <c r="L214" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="M214" s="10">
+        <v>46094.431944444441</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
         <v>191</v>
       </c>
@@ -8064,8 +10664,17 @@
       <c r="C215" s="5">
         <v>46092.777083333334</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K215" s="4">
+        <v>209</v>
+      </c>
+      <c r="L215" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="M215" s="10">
+        <v>46094.428472222222</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>192</v>
       </c>
@@ -8075,8 +10684,17 @@
       <c r="C216" s="5">
         <v>46092.775694444441</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K216" s="4">
+        <v>210</v>
+      </c>
+      <c r="L216" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="M216" s="10">
+        <v>46094.427083333336</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>193</v>
       </c>
@@ -8086,8 +10704,17 @@
       <c r="C217" s="5">
         <v>46092.775000000001</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K217" s="4">
+        <v>211</v>
+      </c>
+      <c r="L217" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="M217" s="10">
+        <v>46094.415972222225</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>194</v>
       </c>
@@ -8097,8 +10724,17 @@
       <c r="C218" s="5">
         <v>46092.775000000001</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K218" s="4">
+        <v>212</v>
+      </c>
+      <c r="L218" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M218" s="10">
+        <v>46094.413888888892</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>195</v>
       </c>
@@ -8108,8 +10744,17 @@
       <c r="C219" s="5">
         <v>46092.775000000001</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K219" s="4">
+        <v>213</v>
+      </c>
+      <c r="L219" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="M219" s="10">
+        <v>46094.413194444445</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
         <v>196</v>
       </c>
@@ -8119,8 +10764,17 @@
       <c r="C220" s="5">
         <v>46092.773611111108</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K220" s="4">
+        <v>214</v>
+      </c>
+      <c r="L220" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M220" s="10">
+        <v>46094.413194444445</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>197</v>
       </c>
@@ -8130,8 +10784,17 @@
       <c r="C221" s="5">
         <v>46092.772222222222</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K221" s="4">
+        <v>215</v>
+      </c>
+      <c r="L221" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="M221" s="10">
+        <v>46094.411805555559</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>198</v>
       </c>
@@ -8141,8 +10804,17 @@
       <c r="C222" s="5">
         <v>46092.771527777775</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K222" s="4">
+        <v>216</v>
+      </c>
+      <c r="L222" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="M222" s="10">
+        <v>46094.407638888886</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>199</v>
       </c>
@@ -8152,8 +10824,17 @@
       <c r="C223" s="5">
         <v>46092.770833333336</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K223" s="3">
+        <v>217</v>
+      </c>
+      <c r="L223" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="M223" s="10">
+        <v>46094.404166666667</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>200</v>
       </c>
@@ -8163,8 +10844,17 @@
       <c r="C224" s="5">
         <v>46092.770138888889</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K224" s="4">
+        <v>218</v>
+      </c>
+      <c r="L224" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="M224" s="10">
+        <v>46094.401388888888</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>201</v>
       </c>
@@ -8174,8 +10864,17 @@
       <c r="C225" s="5">
         <v>46092.769444444442</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K225" s="4">
+        <v>219</v>
+      </c>
+      <c r="L225" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="M225" s="10">
+        <v>46094.398611111108</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>202</v>
       </c>
@@ -8185,8 +10884,17 @@
       <c r="C226" s="5">
         <v>46092.769444444442</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K226" s="4">
+        <v>220</v>
+      </c>
+      <c r="L226" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="M226" s="10">
+        <v>46094.398611111108</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>203</v>
       </c>
@@ -8196,8 +10904,17 @@
       <c r="C227" s="5">
         <v>46092.768750000003</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K227" s="4">
+        <v>221</v>
+      </c>
+      <c r="L227" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="M227" s="10">
+        <v>46094.397222222222</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
         <v>204</v>
       </c>
@@ -8207,8 +10924,17 @@
       <c r="C228" s="5">
         <v>46092.768750000003</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K228" s="4">
+        <v>222</v>
+      </c>
+      <c r="L228" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="M228" s="10">
+        <v>46094.396527777775</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>205</v>
       </c>
@@ -8218,8 +10944,17 @@
       <c r="C229" s="5">
         <v>46092.768055555556</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K229" s="4">
+        <v>223</v>
+      </c>
+      <c r="L229" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="M229" s="10">
+        <v>46094.395138888889</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4">
         <v>206</v>
       </c>
@@ -8229,8 +10964,17 @@
       <c r="C230" s="5">
         <v>46092.768055555556</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K230" s="4">
+        <v>224</v>
+      </c>
+      <c r="L230" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="M230" s="10">
+        <v>46094.394444444442</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>207</v>
       </c>
@@ -8240,8 +10984,17 @@
       <c r="C231" s="5">
         <v>46092.765972222223</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K231" s="4">
+        <v>225</v>
+      </c>
+      <c r="L231" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M231" s="10">
+        <v>46094.393750000003</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>208</v>
       </c>
@@ -8251,8 +11004,17 @@
       <c r="C232" s="5">
         <v>46092.76458333333</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K232" s="4">
+        <v>226</v>
+      </c>
+      <c r="L232" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M232" s="10">
+        <v>46094.393055555556</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>209</v>
       </c>
@@ -8262,8 +11024,17 @@
       <c r="C233" s="5">
         <v>46092.76458333333</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K233" s="4">
+        <v>227</v>
+      </c>
+      <c r="L233" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="M233" s="10">
+        <v>46094.390972222223</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>210</v>
       </c>
@@ -8273,8 +11044,17 @@
       <c r="C234" s="5">
         <v>46092.763194444444</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K234" s="4">
+        <v>228</v>
+      </c>
+      <c r="L234" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="M234" s="10">
+        <v>46094.386111111111</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>211</v>
       </c>
@@ -8284,8 +11064,17 @@
       <c r="C235" s="5">
         <v>46092.763194444444</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K235" s="3">
+        <v>229</v>
+      </c>
+      <c r="L235" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="M235" s="10">
+        <v>46094.385416666664</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
         <v>212</v>
       </c>
@@ -8295,8 +11084,17 @@
       <c r="C236" s="5">
         <v>46092.762499999997</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K236" s="4">
+        <v>230</v>
+      </c>
+      <c r="L236" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="M236" s="10">
+        <v>46094.381944444445</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>213</v>
       </c>
@@ -8306,8 +11104,17 @@
       <c r="C237" s="5">
         <v>46092.762499999997</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K237" s="4">
+        <v>231</v>
+      </c>
+      <c r="L237" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="M237" s="10">
+        <v>46094.381249999999</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>214</v>
       </c>
@@ -8317,8 +11124,17 @@
       <c r="C238" s="5">
         <v>46092.761805555558</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K238" s="4">
+        <v>232</v>
+      </c>
+      <c r="L238" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="M238" s="10">
+        <v>46094.381249999999</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>215</v>
       </c>
@@ -8328,8 +11144,17 @@
       <c r="C239" s="5">
         <v>46092.759722222225</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K239" s="4">
+        <v>233</v>
+      </c>
+      <c r="L239" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="M239" s="10">
+        <v>46094.380555555559</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>216</v>
       </c>
@@ -8339,8 +11164,17 @@
       <c r="C240" s="5">
         <v>46092.759722222225</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K240" s="4">
+        <v>234</v>
+      </c>
+      <c r="L240" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="M240" s="10">
+        <v>46094.379166666666</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>217</v>
       </c>
@@ -8350,8 +11184,17 @@
       <c r="C241" s="5">
         <v>46092.759027777778</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K241" s="4">
+        <v>235</v>
+      </c>
+      <c r="L241" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="M241" s="10">
+        <v>46094.377083333333</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>218</v>
       </c>
@@ -8361,8 +11204,17 @@
       <c r="C242" s="5">
         <v>46092.758333333331</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K242" s="4">
+        <v>236</v>
+      </c>
+      <c r="L242" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="M242" s="10">
+        <v>46094.372916666667</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>219</v>
       </c>
@@ -8372,8 +11224,17 @@
       <c r="C243" s="5">
         <v>46092.758333333331</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K243" s="4">
+        <v>237</v>
+      </c>
+      <c r="L243" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="M243" s="10">
+        <v>46094.368750000001</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>220</v>
       </c>
@@ -8383,8 +11244,17 @@
       <c r="C244" s="5">
         <v>46092.757638888892</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K244" s="4">
+        <v>238</v>
+      </c>
+      <c r="L244" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="M244" s="10">
+        <v>46094.366666666669</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>221</v>
       </c>
@@ -8394,8 +11264,17 @@
       <c r="C245" s="5">
         <v>46092.756249999999</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K245" s="4">
+        <v>239</v>
+      </c>
+      <c r="L245" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="M245" s="10">
+        <v>46094.363888888889</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>222</v>
       </c>
@@ -8405,8 +11284,17 @@
       <c r="C246" s="5">
         <v>46092.755555555559</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K246" s="4">
+        <v>240</v>
+      </c>
+      <c r="L246" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="M246" s="10">
+        <v>46094.361111111109</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>223</v>
       </c>
@@ -8416,8 +11304,17 @@
       <c r="C247" s="5">
         <v>46092.754861111112</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K247" s="3">
+        <v>241</v>
+      </c>
+      <c r="L247" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="M247" s="10">
+        <v>46094.36041666667</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>224</v>
       </c>
@@ -8427,8 +11324,17 @@
       <c r="C248" s="5">
         <v>46092.754166666666</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K248" s="4">
+        <v>242</v>
+      </c>
+      <c r="L248" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="M248" s="10">
+        <v>46094.36041666667</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>225</v>
       </c>
@@ -8438,8 +11344,17 @@
       <c r="C249" s="5">
         <v>46092.753472222219</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K249" s="4">
+        <v>243</v>
+      </c>
+      <c r="L249" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="M249" s="10">
+        <v>46094.359722222223</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>226</v>
       </c>
@@ -8449,8 +11364,17 @@
       <c r="C250" s="5">
         <v>46092.753472222219</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K250" s="4">
+        <v>244</v>
+      </c>
+      <c r="L250" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="M250" s="10">
+        <v>46094.332638888889</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>227</v>
       </c>
@@ -8460,8 +11384,17 @@
       <c r="C251" s="5">
         <v>46092.75277777778</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K251" s="4">
+        <v>245</v>
+      </c>
+      <c r="L251" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="M251" s="10">
+        <v>46094.331944444442</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>228</v>
       </c>
@@ -8471,8 +11404,17 @@
       <c r="C252" s="5">
         <v>46092.748611111114</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K252" s="4">
+        <v>246</v>
+      </c>
+      <c r="L252" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="M252" s="10">
+        <v>46094.331944444442</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>229</v>
       </c>
@@ -8482,8 +11424,17 @@
       <c r="C253" s="5">
         <v>46092.748611111114</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K253" s="4">
+        <v>247</v>
+      </c>
+      <c r="L253" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="M253" s="10">
+        <v>46094.322222222225</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>230</v>
       </c>
@@ -8493,8 +11444,17 @@
       <c r="C254" s="5">
         <v>46092.748611111114</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K254" s="4">
+        <v>248</v>
+      </c>
+      <c r="L254" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="M254" s="10">
+        <v>46094.321527777778</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>231</v>
       </c>
@@ -8504,8 +11464,17 @@
       <c r="C255" s="5">
         <v>46092.747916666667</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K255" s="4">
+        <v>249</v>
+      </c>
+      <c r="L255" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="M255" s="10">
+        <v>46094.320833333331</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>232</v>
       </c>
@@ -8515,8 +11484,17 @@
       <c r="C256" s="5">
         <v>46092.74722222222</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K256" s="4">
+        <v>250</v>
+      </c>
+      <c r="L256" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="M256" s="10">
+        <v>46094.320138888892</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>233</v>
       </c>
@@ -8526,8 +11504,17 @@
       <c r="C257" s="5">
         <v>46092.74722222222</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K257" s="4">
+        <v>251</v>
+      </c>
+      <c r="L257" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="M257" s="10">
+        <v>46094.308333333334</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>234</v>
       </c>
@@ -8537,8 +11524,17 @@
       <c r="C258" s="5">
         <v>46092.746527777781</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K258" s="4">
+        <v>252</v>
+      </c>
+      <c r="L258" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="M258" s="10">
+        <v>46094.306944444441</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>235</v>
       </c>
@@ -8549,7 +11545,7 @@
         <v>46092.745833333334</v>
       </c>
     </row>
-    <row r="260" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>236</v>
       </c>
@@ -8560,7 +11556,7 @@
         <v>46092.745138888888</v>
       </c>
     </row>
-    <row r="261" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>237</v>
       </c>
@@ -8571,7 +11567,7 @@
         <v>46092.743055555555</v>
       </c>
     </row>
-    <row r="262" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>238</v>
       </c>
@@ -8582,7 +11578,7 @@
         <v>46092.743055555555</v>
       </c>
     </row>
-    <row r="263" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>239</v>
       </c>
@@ -8593,7 +11589,7 @@
         <v>46092.741666666669</v>
       </c>
     </row>
-    <row r="264" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>240</v>
       </c>
@@ -8604,7 +11600,7 @@
         <v>46092.741666666669</v>
       </c>
     </row>
-    <row r="265" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>241</v>
       </c>
@@ -8615,7 +11611,7 @@
         <v>46092.741666666669</v>
       </c>
     </row>
-    <row r="266" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>242</v>
       </c>
@@ -8626,7 +11622,7 @@
         <v>46092.740277777775</v>
       </c>
     </row>
-    <row r="267" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>243</v>
       </c>
@@ -8637,7 +11633,7 @@
         <v>46092.738194444442</v>
       </c>
     </row>
-    <row r="268" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>244</v>
       </c>
@@ -8648,7 +11644,7 @@
         <v>46092.736805555556</v>
       </c>
     </row>
-    <row r="269" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>245</v>
       </c>
@@ -8659,7 +11655,7 @@
         <v>46092.736805555556</v>
       </c>
     </row>
-    <row r="270" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>246</v>
       </c>
@@ -8670,7 +11666,7 @@
         <v>46092.736805555556</v>
       </c>
     </row>
-    <row r="271" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>247</v>
       </c>
@@ -8681,7 +11677,7 @@
         <v>46092.736805555556</v>
       </c>
     </row>
-    <row r="272" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>248</v>
       </c>
